--- a/output/screening_result.xlsx
+++ b/output/screening_result.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,202 +429,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>candidate_level</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>candidate_score</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MA20</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>是否站上 MA20</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>K 值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>D 值</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA5</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA20</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA40</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>放量倍數</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MACD_DIF</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MACD_Signal</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MACD_Histogram</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前1日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前2日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MACD_綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>是否符合 KD 區間</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>是否符合 RSI 區間</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>是否明顯放量</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MACD 是否綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>法人近 5 日是否合計買超</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>投信近 5 日是否買超</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>外資近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>投信近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>自營商近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>三大法人近 1 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>外資近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>投信近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>自營商近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>三大法人近 5 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>外資近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>投信近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>自營商近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>三大法人近 20 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
         </is>
@@ -673,19 +685,19 @@
         <v>1.839402433396137</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05707517759306668</v>
+        <v>0.0570751775930666</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.002957888560102742</v>
+        <v>-0.0029578885601027</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06003306615316942</v>
+        <v>0.0600330661531694</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08140312991042646</v>
+        <v>0.08140312991042641</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1191330164089761</v>
+        <v>0.119133016408976</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -819,19 +831,19 @@
         <v>1.580724998413493</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1808840313655367</v>
+        <v>-0.1808840313655366</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1408225222788201</v>
+        <v>-0.14082252227882</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.04006150908671657</v>
+        <v>-0.0400615090867165</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05093762199336851</v>
+        <v>-0.0509376219933685</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05194541608982742</v>
+        <v>-0.0519454160898274</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -971,13 +983,13 @@
         <v>-0.4985450554719721</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04336846687852813</v>
+        <v>0.0433684668785281</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04526563362469704</v>
+        <v>0.045265633624697</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05191589189844181</v>
+        <v>0.0519158918984418</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1117,13 +1129,13 @@
         <v>-0.7662871133930196</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05304759902012179</v>
+        <v>0.0530475990201217</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05140381760834511</v>
+        <v>0.0514038176083451</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06091183394929145</v>
+        <v>0.0609118339492914</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1260,16 +1272,16 @@
         <v>-0.038684783307672</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07277598983752707</v>
+        <v>-0.07277598983752701</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03409120652985508</v>
+        <v>0.034091206529855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03959072830204988</v>
+        <v>0.0395907283020498</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03910897843283044</v>
+        <v>0.0391089784328304</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1412,10 +1424,10 @@
         <v>-0.0249666651297922</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.02023013043446435</v>
+        <v>-0.0202301304344643</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.008345501526961507</v>
+        <v>-0.0083455015269615</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1555,7 +1567,7 @@
         <v>-0.3800329123209913</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.06135081899517369</v>
+        <v>-0.0613508189951736</v>
       </c>
       <c r="S8" t="n">
         <v>-0.09689548365965001</v>
@@ -1695,19 +1707,19 @@
         <v>1.798804727870702</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2419575748652605</v>
+        <v>-0.2419575748652604</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1266850911670767</v>
+        <v>-0.1266850911670766</v>
       </c>
       <c r="R9" t="n">
         <v>-0.1152724836981838</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09662280170647791</v>
+        <v>-0.0966228017064779</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.01663634277134032</v>
+        <v>-0.0166363427713403</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1841,19 +1853,19 @@
         <v>1.7832781618118</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.005917047706663681</v>
+        <v>-0.0059170477066636</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.07419920651975694</v>
+        <v>-0.07419920651975689</v>
       </c>
       <c r="R10" t="n">
-        <v>0.06828215881309325</v>
+        <v>0.0682821588130932</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08930145589692245</v>
+        <v>0.0893014558969224</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1217865254905505</v>
+        <v>0.1217865254905504</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1996,7 +2008,7 @@
         <v>0.3776729282985334</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4825700324428605</v>
+        <v>0.4825700324428604</v>
       </c>
       <c r="T11" t="n">
         <v>0.662287037074081</v>
@@ -2136,7 +2148,7 @@
         <v>0.3598539212373666</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2020636183624591</v>
+        <v>0.202063618362459</v>
       </c>
       <c r="R12" t="n">
         <v>0.1577903028749075</v>
@@ -2282,16 +2294,16 @@
         <v>-0.3881676954178754</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.431135773024979</v>
+        <v>-0.4311357730249789</v>
       </c>
       <c r="R13" t="n">
-        <v>0.04296807760710353</v>
+        <v>0.0429680776071035</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00374273470610087</v>
+        <v>0.0037427347061008</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.02217975833307273</v>
+        <v>-0.0221797583330727</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2425,19 +2437,19 @@
         <v>1.635955388215924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.04252266497129398</v>
+        <v>0.0425226649712939</v>
       </c>
       <c r="Q14" t="n">
         <v>0.1163449674426191</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.07382230247132515</v>
+        <v>-0.0738223024713251</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.04122709533962188</v>
+        <v>-0.0412270953396218</v>
       </c>
       <c r="T14" t="n">
-        <v>0.002082373979241658</v>
+        <v>0.0020823739792416</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2580,10 +2592,10 @@
         <v>-0.06671035967326749</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.05169010730895907</v>
+        <v>-0.051690107308959</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.01237562072793957</v>
+        <v>-0.0123756207279395</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2696,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>30.18586796019645</v>
+        <v>30.18586796019646</v>
       </c>
       <c r="J16" t="n">
         <v>45.14705019354905</v>
@@ -2726,10 +2738,10 @@
         <v>-0.2046288617528741</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.05205642433026325</v>
+        <v>-0.0520564243302632</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1062483856006611</v>
+        <v>0.106248385600661</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2860,7 +2872,7 @@
         <v>5389496.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.896273292690601</v>
+        <v>1.896273292690602</v>
       </c>
       <c r="P17" t="n">
         <v>0.4038925206493076</v>
@@ -2872,10 +2884,10 @@
         <v>0.116457645451703</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4941181782478166</v>
+        <v>0.4941181782478165</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9293924714675723</v>
+        <v>0.9293924714675724</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2988,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>30.53242543371862</v>
+        <v>30.53242543371863</v>
       </c>
       <c r="J18" t="n">
         <v>41.61517745627029</v>
@@ -3015,13 +3027,13 @@
         <v>-0.4106534675819211</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.08040273606741488</v>
+        <v>-0.0804027360674148</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.04073207890847924</v>
+        <v>-0.0407320789084792</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03164810210110147</v>
+        <v>0.0316481021011014</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3161,13 +3173,13 @@
         <v>-0.3359433016543629</v>
       </c>
       <c r="R19" t="n">
-        <v>0.06458651840347929</v>
+        <v>0.0645865184034792</v>
       </c>
       <c r="S19" t="n">
-        <v>0.06947599190700904</v>
+        <v>0.069475991907009</v>
       </c>
       <c r="T19" t="n">
-        <v>0.09695122744569268</v>
+        <v>0.09695122744569259</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -3307,13 +3319,13 @@
         <v>0.256726040843972</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.04401885643618519</v>
+        <v>-0.0440188564361851</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.01763998701829256</v>
+        <v>-0.0176399870182925</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01184571612104895</v>
+        <v>0.0118457161210489</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3447,19 +3459,19 @@
         <v>1.525494998136593</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.06302702848723207</v>
+        <v>-0.063027028487232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.03444490503477615</v>
+        <v>-0.0344449050347761</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.02858212345245592</v>
+        <v>-0.0285821234524559</v>
       </c>
       <c r="S21" t="n">
-        <v>0.002827214278937951</v>
+        <v>0.0028272142789379</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01440908807375371</v>
+        <v>0.0144090880737537</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3596,16 +3608,16 @@
         <v>-0.1481337758828047</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1451000600982614</v>
+        <v>-0.1451000600982613</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.003033715784543367</v>
+        <v>-0.0030337157845433</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.006370086530677693</v>
+        <v>-0.0063700865306776</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.009060828894512735</v>
+        <v>-0.0090608288945127</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3745,13 +3757,13 @@
         <v>-1.312189918065065</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3244853267880852</v>
+        <v>0.3244853267880851</v>
       </c>
       <c r="S23" t="n">
         <v>0.3180542302507319</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3014591542416836</v>
+        <v>0.3014591542416835</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3891,13 +3903,13 @@
         <v>-0.2724307945518312</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.02852609044847937</v>
+        <v>-0.0285260904484793</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.01496776097232111</v>
+        <v>-0.0149677609723211</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.008588931923730447</v>
+        <v>-0.008588931923730401</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -4031,19 +4043,19 @@
         <v>1.003173868321978</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.06332718323102426</v>
+        <v>-0.06332718323102419</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.03359213917101796</v>
+        <v>-0.0335921391710179</v>
       </c>
       <c r="R25" t="n">
         <v>-0.0297350440600063</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.02997532303726926</v>
+        <v>-0.0299753230372692</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.05292571016015371</v>
+        <v>-0.0529257101601537</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4177,19 +4189,19 @@
         <v>0.96482269131437</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1351788962546561</v>
+        <v>-0.135178896254656</v>
       </c>
       <c r="Q26" t="n">
         <v>-0.1280823181746952</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.007096578079960836</v>
+        <v>-0.0070965780799608</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.02687530782058334</v>
+        <v>-0.0268753078205833</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.04416464935125755</v>
+        <v>-0.0441646493512575</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -4320,22 +4332,22 @@
         <v>1125916.225</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9105588305876801</v>
+        <v>0.9105588305876799</v>
       </c>
       <c r="P27" t="n">
         <v>-0.0184294891631076</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.02050138599078901</v>
+        <v>-0.020501385990789</v>
       </c>
       <c r="R27" t="n">
-        <v>0.00207189682768141</v>
+        <v>0.0020718968276814</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002602296497784571</v>
+        <v>0.0026022964977845</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003536614594513193</v>
+        <v>0.0035366145945131</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4469,19 +4481,19 @@
         <v>0.3081990758454248</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.03334931484251857</v>
+        <v>-0.0333493148425185</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.01046773277712322</v>
+        <v>-0.0104677327771232</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.02288158206539535</v>
+        <v>-0.0228815820653953</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.02567799944667791</v>
+        <v>-0.0256779994466779</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.02690468446860406</v>
+        <v>-0.026904684468604</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4588,7 +4600,7 @@
         <v>27.5</v>
       </c>
       <c r="G29" t="n">
-        <v>28.71749992370605</v>
+        <v>28.71749992370606</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -4615,7 +4627,7 @@
         <v>2.125165839050832</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.1101141161981012</v>
+        <v>-0.1101141161981011</v>
       </c>
       <c r="Q29" t="n">
         <v>0.114495724853119</v>
@@ -4904,7 +4916,7 @@
         <v>158878.775</v>
       </c>
       <c r="O31" t="n">
-        <v>1.837621951233754</v>
+        <v>1.837621951233753</v>
       </c>
       <c r="P31" t="n">
         <v>-0.303341141391666</v>
@@ -4913,13 +4925,13 @@
         <v>-0.5186348610355919</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2152937196439259</v>
+        <v>0.2152937196439258</v>
       </c>
       <c r="S31" t="n">
         <v>0.2587159426150786</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2485007574791648</v>
+        <v>0.2485007574791647</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -5059,13 +5071,13 @@
         <v>-0.1667161311207628</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.03438024783712951</v>
+        <v>-0.0343802478371295</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.07952984104989819</v>
+        <v>-0.0795298410498981</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.09679417573719046</v>
+        <v>-0.0967941757371904</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -5351,13 +5363,13 @@
         <v>-0.0903966745737473</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.03258721900541321</v>
+        <v>-0.0325872190054132</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.001717367964322009</v>
+        <v>-0.001717367964322</v>
       </c>
       <c r="T34" t="n">
-        <v>0.00814664426163085</v>
+        <v>0.0081466442616308</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5497,13 +5509,13 @@
         <v>-0.2935732383990579</v>
       </c>
       <c r="R35" t="n">
-        <v>0.04794177147055367</v>
+        <v>0.0479417714705536</v>
       </c>
       <c r="S35" t="n">
-        <v>0.04320541528264987</v>
+        <v>0.0432054152826498</v>
       </c>
       <c r="T35" t="n">
-        <v>0.05175250589301905</v>
+        <v>0.051752505893019</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5643,13 +5655,13 @@
         <v>-0.9542266912467944</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.08771832645632649</v>
+        <v>-0.08771832645632641</v>
       </c>
       <c r="S36" t="n">
         <v>-0.0869277373098295</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.07501743440886655</v>
+        <v>-0.0750174344088665</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5792,10 +5804,10 @@
         <v>-0.9152645595746156</v>
       </c>
       <c r="S37" t="n">
-        <v>-0.9486018252643413</v>
+        <v>-0.9486018252643412</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.2695243893553894</v>
+        <v>-0.2695243893553893</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5857,7 +5869,7 @@
         <v>-561.461</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-922.3249999999999</v>
+        <v>-922.325</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -5929,16 +5941,16 @@
         <v>1.523473055739829</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.002821873993433144</v>
+        <v>-0.0028218739934331</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.06410956955032149</v>
+        <v>-0.0641095695503214</v>
       </c>
       <c r="R38" t="n">
-        <v>0.06128769555688834</v>
+        <v>0.0612876955568883</v>
       </c>
       <c r="S38" t="n">
-        <v>0.09929104468963655</v>
+        <v>0.0992910446896365</v>
       </c>
       <c r="T38" t="n">
         <v>0.1476838546539809</v>
@@ -6224,16 +6236,16 @@
         <v>-0.2269263504303893</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.2314013296597059</v>
+        <v>-0.2314013296597058</v>
       </c>
       <c r="R40" t="n">
-        <v>0.004474979229316528</v>
+        <v>0.0044749792293165</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.02490320946406871</v>
+        <v>-0.0249032094640687</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.03576408482575447</v>
+        <v>-0.0357640848257544</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6367,19 +6379,19 @@
         <v>1.43446646883085</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.01315781132596072</v>
+        <v>-0.0131578113259607</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2489182445671212</v>
+        <v>0.2489182445671211</v>
       </c>
       <c r="R41" t="n">
         <v>-0.2620760558930819</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.1453064809411631</v>
+        <v>-0.145306480941163</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.04815400939448922</v>
+        <v>-0.0481540093944892</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6516,7 +6528,7 @@
         <v>-0.260311710181341</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.4066925966822941</v>
+        <v>-0.406692596682294</v>
       </c>
       <c r="R42" t="n">
         <v>0.146380886500953</v>
@@ -6525,7 +6537,7 @@
         <v>0.2071291220801476</v>
       </c>
       <c r="T42" t="n">
-        <v>0.242265375992006</v>
+        <v>0.2422653759920059</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6659,10 +6671,10 @@
         <v>1.414631500155851</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.09520171982933334</v>
+        <v>-0.0952017198293333</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2468707643551459</v>
+        <v>0.2468707643551458</v>
       </c>
       <c r="R43" t="n">
         <v>-0.3420724841844792</v>
@@ -6671,7 +6683,7 @@
         <v>-0.3131464164646977</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.1947314191951318</v>
+        <v>-0.1947314191951317</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -6802,7 +6814,7 @@
         <v>43862</v>
       </c>
       <c r="O44" t="n">
-        <v>1.381644559510172</v>
+        <v>1.381644559510173</v>
       </c>
       <c r="P44" t="n">
         <v>-1.644154325531758</v>
@@ -6957,13 +6969,13 @@
         <v>-0.6887826229136117</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09018362819220516</v>
+        <v>0.0901836281922051</v>
       </c>
       <c r="S45" t="n">
-        <v>0.09022867952628122</v>
+        <v>0.09022867952628121</v>
       </c>
       <c r="T45" t="n">
-        <v>0.1134644690749076</v>
+        <v>0.1134644690749075</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7097,19 +7109,19 @@
         <v>1.340713262650776</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1678286692455693</v>
+        <v>0.1678286692455692</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1847590204761862</v>
+        <v>0.1847590204761861</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.0169303512306169</v>
+        <v>-0.0169303512306168</v>
       </c>
       <c r="S46" t="n">
-        <v>0.01600186697586498</v>
+        <v>0.0160018669758649</v>
       </c>
       <c r="T46" t="n">
-        <v>0.07463827441465035</v>
+        <v>0.0746382744146503</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7243,16 +7255,16 @@
         <v>1.325407881462036</v>
       </c>
       <c r="P47" t="n">
-        <v>0.009704539192306072</v>
+        <v>0.009704539192306001</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.02457551877163998</v>
+        <v>-0.0245755187716399</v>
       </c>
       <c r="R47" t="n">
-        <v>0.03428005796394605</v>
+        <v>0.034280057963946</v>
       </c>
       <c r="S47" t="n">
-        <v>0.07140723864166555</v>
+        <v>0.0714072386416655</v>
       </c>
       <c r="T47" t="n">
         <v>0.1200608172714291</v>
@@ -7395,10 +7407,10 @@
         <v>-0.7451304069886938</v>
       </c>
       <c r="R48" t="n">
-        <v>0.02875490875487763</v>
+        <v>0.0287549087548776</v>
       </c>
       <c r="S48" t="n">
-        <v>0.05789699160078599</v>
+        <v>0.0578969916007859</v>
       </c>
       <c r="T48" t="n">
         <v>0.1104923900681894</v>
@@ -7541,13 +7553,13 @@
         <v>-1.744359638676258</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.08298486444700637</v>
+        <v>-0.0829848644470063</v>
       </c>
       <c r="S49" t="n">
-        <v>-0.1355131032599302</v>
+        <v>-0.1355131032599301</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.1930966195847468</v>
+        <v>-0.1930966195847467</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7681,19 +7693,19 @@
         <v>1.28115306772091</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.3888881856668434</v>
+        <v>-0.3888881856668433</v>
       </c>
       <c r="Q50" t="n">
         <v>-0.3328958859890168</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.05599229967782654</v>
+        <v>-0.0559922996778265</v>
       </c>
       <c r="S50" t="n">
-        <v>-0.06614592339677605</v>
+        <v>-0.066145923396776</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.07217485039420335</v>
+        <v>-0.07217485039420329</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7827,19 +7839,19 @@
         <v>1.240810864329066</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.05570595249982624</v>
+        <v>-0.0557059524998262</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.0742800960870406</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01857414358721436</v>
+        <v>0.0185741435872143</v>
       </c>
       <c r="S51" t="n">
-        <v>0.01668428170683153</v>
+        <v>0.0166842817068315</v>
       </c>
       <c r="T51" t="n">
-        <v>-0.01712381353649825</v>
+        <v>-0.0171238135364982</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -7979,13 +7991,13 @@
         <v>-0.2790708529521356</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.03854497710318128</v>
+        <v>-0.0385449771031812</v>
       </c>
       <c r="S52" t="n">
-        <v>-0.002399427678093979</v>
+        <v>-0.0023994276780939</v>
       </c>
       <c r="T52" t="n">
-        <v>0.02375228502969762</v>
+        <v>0.0237522850296976</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8044,7 +8056,7 @@
         <v>-2.344</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.1560000000000006</v>
+        <v>0.1560000000000005</v>
       </c>
       <c r="AJ52" t="n">
         <v>31.86</v>
@@ -8119,16 +8131,16 @@
         <v>1.198011196029598</v>
       </c>
       <c r="P53" t="n">
-        <v>0.004120599986180196</v>
+        <v>0.0041205999861801</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.01432192550611949</v>
+        <v>-0.0143219255061194</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01844252549229968</v>
+        <v>0.0184425254922996</v>
       </c>
       <c r="S53" t="n">
-        <v>0.09111258937696368</v>
+        <v>0.09111258937696361</v>
       </c>
       <c r="T53" t="n">
         <v>0.1488003391996831</v>
@@ -8274,7 +8286,7 @@
         <v>-0.4089015225913984</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.3406516827308617</v>
+        <v>-0.3406516827308616</v>
       </c>
       <c r="T54" t="n">
         <v>-0.2072290987675836</v>
@@ -8411,19 +8423,19 @@
         <v>0.9495123450491636</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.9082974689741405</v>
+        <v>-0.9082974689741404</v>
       </c>
       <c r="Q55" t="n">
         <v>-0.8889721184411055</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.01932535053303508</v>
+        <v>-0.019325350533035</v>
       </c>
       <c r="S55" t="n">
-        <v>-0.06494275914383318</v>
+        <v>-0.0649427591438331</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.08888607844110752</v>
+        <v>-0.0888860784411075</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8563,10 +8575,10 @@
         <v>-0.6609626253823604</v>
       </c>
       <c r="R56" t="n">
-        <v>0.06813888047874861</v>
+        <v>0.0681388804787486</v>
       </c>
       <c r="S56" t="n">
-        <v>0.1008923160634631</v>
+        <v>0.100892316063463</v>
       </c>
       <c r="T56" t="n">
         <v>0.124027458424071</v>
@@ -8852,7 +8864,7 @@
         <v>0.4437671585590763</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.1677740635469122</v>
+        <v>0.1677740635469121</v>
       </c>
       <c r="R58" t="n">
         <v>0.2759930950121642</v>
@@ -8977,7 +8989,7 @@
         <v>39.19161417957683</v>
       </c>
       <c r="J59" t="n">
-        <v>28.48365925360274</v>
+        <v>28.48365925360273</v>
       </c>
       <c r="K59" t="n">
         <v>24.56157188356397</v>
@@ -9007,7 +9019,7 @@
         <v>-0.1364299700650431</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.2232740689086299</v>
+        <v>-0.2232740689086298</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -9257,7 +9269,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>99.19999694824219</v>
+        <v>99.1999969482422</v>
       </c>
       <c r="G61" t="n">
         <v>99.53500022888184</v>
@@ -9296,10 +9308,10 @@
         <v>-0.1487675186313835</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.08198202307414848</v>
+        <v>-0.0819820230741484</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.04213063596094624</v>
+        <v>-0.0421306359609462</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -9436,16 +9448,16 @@
         <v>0.2013740750501469</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.1220078887518429</v>
+        <v>0.1220078887518428</v>
       </c>
       <c r="R62" t="n">
-        <v>0.07936618629830404</v>
+        <v>0.079366186298304</v>
       </c>
       <c r="S62" t="n">
         <v>-0.1137881662573722</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.1033808123851388</v>
+        <v>-0.1033808123851387</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -9585,13 +9597,13 @@
         <v>-1.04579931371177</v>
       </c>
       <c r="R63" t="n">
-        <v>-0.03020957886800346</v>
+        <v>-0.0302095788680034</v>
       </c>
       <c r="S63" t="n">
-        <v>-0.1238112854771514</v>
+        <v>-0.1238112854771513</v>
       </c>
       <c r="T63" t="n">
-        <v>-0.1458734728691891</v>
+        <v>-0.145873472869189</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -9704,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>13.27282771460793</v>
+        <v>13.27282771460794</v>
       </c>
       <c r="J64" t="n">
         <v>15.72798670235252</v>
@@ -9731,13 +9743,13 @@
         <v>-0.5193139278924654</v>
       </c>
       <c r="R64" t="n">
-        <v>-0.06815659551818243</v>
+        <v>-0.0681565955181824</v>
       </c>
       <c r="S64" t="n">
-        <v>-0.06804932552052112</v>
+        <v>-0.06804932552052111</v>
       </c>
       <c r="T64" t="n">
-        <v>-0.02942642255870948</v>
+        <v>-0.0294264225587094</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -9871,19 +9883,19 @@
         <v>1.37898931550765</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.01453945324268346</v>
+        <v>-0.0145394532426834</v>
       </c>
       <c r="Q65" t="n">
-        <v>-0.08802936976482212</v>
+        <v>-0.0880293697648221</v>
       </c>
       <c r="R65" t="n">
-        <v>0.07348991652213865</v>
+        <v>0.0734899165221386</v>
       </c>
       <c r="S65" t="n">
-        <v>0.07750027075102853</v>
+        <v>0.0775002707510285</v>
       </c>
       <c r="T65" t="n">
-        <v>0.06878276824500457</v>
+        <v>0.0687827682450045</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -10023,10 +10035,10 @@
         <v>-0.5122927222630316</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.1334825158475135</v>
+        <v>-0.1334825158475134</v>
       </c>
       <c r="S66" t="n">
-        <v>-0.09961932821432845</v>
+        <v>-0.0996193282143284</v>
       </c>
       <c r="T66" t="n">
         <v>-0.0302942136827089</v>
@@ -10172,7 +10184,7 @@
         <v>-0.3080662720564682</v>
       </c>
       <c r="S67" t="n">
-        <v>-0.2965847479391686</v>
+        <v>-0.2965847479391685</v>
       </c>
       <c r="T67" t="n">
         <v>-0.2093121514365122</v>
@@ -10318,7 +10330,7 @@
         <v>0.2702761204300148</v>
       </c>
       <c r="S68" t="n">
-        <v>0.2798058129214102</v>
+        <v>0.2798058129214101</v>
       </c>
       <c r="T68" t="n">
         <v>0.2138849747076076</v>
@@ -10437,7 +10449,7 @@
         <v>29.00532850935085</v>
       </c>
       <c r="J69" t="n">
-        <v>24.62943694085086</v>
+        <v>24.62943694085087</v>
       </c>
       <c r="K69" t="n">
         <v>42.40217427289991</v>
@@ -10458,16 +10470,16 @@
         <v>-0.2438031422359863</v>
       </c>
       <c r="Q69" t="n">
-        <v>-0.2289982268268628</v>
+        <v>-0.2289982268268627</v>
       </c>
       <c r="R69" t="n">
-        <v>-0.01480491540912354</v>
+        <v>-0.0148049154091235</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.02873366415693418</v>
+        <v>-0.0287336641569341</v>
       </c>
       <c r="T69" t="n">
-        <v>-0.04018509761924732</v>
+        <v>-0.0401850976192473</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -10601,19 +10613,19 @@
         <v>1.296574206191168</v>
       </c>
       <c r="P70" t="n">
-        <v>-0.3969813378884908</v>
+        <v>-0.3969813378884907</v>
       </c>
       <c r="Q70" t="n">
         <v>-0.3712324202807319</v>
       </c>
       <c r="R70" t="n">
-        <v>-0.02574891760775888</v>
+        <v>-0.0257489176077588</v>
       </c>
       <c r="S70" t="n">
-        <v>-0.04081197882338888</v>
+        <v>-0.0408119788233888</v>
       </c>
       <c r="T70" t="n">
-        <v>-0.04594307391703356</v>
+        <v>-0.0459430739170335</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -10821,7 +10833,7 @@
         <v>16.329</v>
       </c>
       <c r="AJ71" t="n">
-        <v>92.58300000000001</v>
+        <v>92.583</v>
       </c>
       <c r="AK71" t="n">
         <v>0</v>
@@ -10899,13 +10911,13 @@
         <v>-0.09146955421090169</v>
       </c>
       <c r="R72" t="n">
-        <v>0.001282960254139598</v>
+        <v>0.0012829602541395</v>
       </c>
       <c r="S72" t="n">
-        <v>0.008886413911057989</v>
+        <v>0.0088864139110579</v>
       </c>
       <c r="T72" t="n">
-        <v>0.01651845140713303</v>
+        <v>0.016518451407133</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -11042,16 +11054,16 @@
         <v>-0.1986627672208634</v>
       </c>
       <c r="Q73" t="n">
-        <v>-0.07458934626741741</v>
+        <v>-0.07458934626741739</v>
       </c>
       <c r="R73" t="n">
-        <v>-0.124073420953446</v>
+        <v>-0.1240734209534459</v>
       </c>
       <c r="S73" t="n">
-        <v>-0.08172192532351477</v>
+        <v>-0.0817219253235147</v>
       </c>
       <c r="T73" t="n">
-        <v>-0.03213790003555367</v>
+        <v>-0.0321379000355536</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -11194,10 +11206,10 @@
         <v>-0.0337716413234817</v>
       </c>
       <c r="S74" t="n">
-        <v>-0.03779790800102334</v>
+        <v>-0.0377979080010233</v>
       </c>
       <c r="T74" t="n">
-        <v>-0.0498603171619097</v>
+        <v>-0.0498603171619096</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -11331,19 +11343,19 @@
         <v>1.20745786778005</v>
       </c>
       <c r="P75" t="n">
-        <v>-0.04918992523716526</v>
+        <v>-0.0491899252371652</v>
       </c>
       <c r="Q75" t="n">
-        <v>-0.002476350378548896</v>
+        <v>-0.0024763503785488</v>
       </c>
       <c r="R75" t="n">
-        <v>-0.04671357485861636</v>
+        <v>-0.0467135748586163</v>
       </c>
       <c r="S75" t="n">
-        <v>-0.05146954958609007</v>
+        <v>-0.05146954958609</v>
       </c>
       <c r="T75" t="n">
-        <v>-0.04979578161098822</v>
+        <v>-0.0497957816109882</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -11486,7 +11498,7 @@
         <v>-0.0238995398730405</v>
       </c>
       <c r="S76" t="n">
-        <v>-0.03399371352818775</v>
+        <v>-0.0339937135281877</v>
       </c>
       <c r="T76" t="n">
         <v>-0.07709330811998499</v>
@@ -11623,19 +11635,19 @@
         <v>1.154899945711243</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.1906615946628634</v>
+        <v>-0.1906615946628633</v>
       </c>
       <c r="Q77" t="n">
-        <v>-0.2451463397457728</v>
+        <v>-0.2451463397457727</v>
       </c>
       <c r="R77" t="n">
         <v>0.0544847450829094</v>
       </c>
       <c r="S77" t="n">
-        <v>0.07617478882841211</v>
+        <v>0.0761747888284121</v>
       </c>
       <c r="T77" t="n">
-        <v>0.1081731766624207</v>
+        <v>0.1081731766624206</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -11703,7 +11715,7 @@
         <v>217</v>
       </c>
       <c r="AL77" t="n">
-        <v>23.10900000000009</v>
+        <v>23.1090000000001</v>
       </c>
       <c r="AM77" t="n">
         <v>-10753.257</v>
@@ -11775,10 +11787,10 @@
         <v>1.129502847612775</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.1987729035799415</v>
+        <v>-0.1987729035799414</v>
       </c>
       <c r="S78" t="n">
-        <v>-0.0009894930271550084</v>
+        <v>-0.000989493027155</v>
       </c>
       <c r="T78" t="n">
         <v>0.328041528335933</v>
@@ -11837,7 +11849,7 @@
         <v>69.36499999999999</v>
       </c>
       <c r="AH78" t="n">
-        <v>-968.2829999999999</v>
+        <v>-968.283</v>
       </c>
       <c r="AI78" t="n">
         <v>-17562.534</v>
@@ -12067,13 +12079,13 @@
         <v>-0.1856721987206606</v>
       </c>
       <c r="R80" t="n">
-        <v>-0.01192555654418206</v>
+        <v>-0.011925556544182</v>
       </c>
       <c r="S80" t="n">
-        <v>-0.02569536440434408</v>
+        <v>-0.025695364404344</v>
       </c>
       <c r="T80" t="n">
-        <v>-0.03267622221472419</v>
+        <v>-0.0326762222147241</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -12216,10 +12228,10 @@
         <v>-0.0164712329819181</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.02100156041681162</v>
+        <v>-0.0210015604168116</v>
       </c>
       <c r="T81" t="n">
-        <v>-0.0242133394541208</v>
+        <v>-0.0242133394541207</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -12359,7 +12371,7 @@
         <v>-5.363531062892289</v>
       </c>
       <c r="R82" t="n">
-        <v>-0.01363398268947336</v>
+        <v>-0.0136339826894733</v>
       </c>
       <c r="S82" t="n">
         <v>-0.2907488373747613</v>
@@ -12469,7 +12481,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>91.19999694824219</v>
+        <v>91.1999969482422</v>
       </c>
       <c r="G83" t="n">
         <v>88.19500007629395</v>
@@ -12499,7 +12511,7 @@
         <v>2.177625421066826</v>
       </c>
       <c r="P83" t="n">
-        <v>0.2123990647558998</v>
+        <v>0.2123990647558997</v>
       </c>
       <c r="Q83" t="n">
         <v>-0.5076708260419354</v>
@@ -12570,7 +12582,7 @@
         <v>-0.6099999999999999</v>
       </c>
       <c r="AI83" t="n">
-        <v>-0.1099999999999959</v>
+        <v>-0.1099999999999958</v>
       </c>
       <c r="AJ83" t="n">
         <v>-162.158</v>
@@ -12651,13 +12663,13 @@
         <v>-0.4439444866145415</v>
       </c>
       <c r="R84" t="n">
-        <v>0.03872435310118477</v>
+        <v>0.0387243531011847</v>
       </c>
       <c r="S84" t="n">
-        <v>-0.05912278007257576</v>
+        <v>-0.0591227800725757</v>
       </c>
       <c r="T84" t="n">
-        <v>-0.1110358990224679</v>
+        <v>-0.1110358990224678</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -12791,10 +12803,10 @@
         <v>1.765449038313258</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.01101717058839213</v>
+        <v>-0.0110171705883921</v>
       </c>
       <c r="Q85" t="n">
-        <v>-0.1306607051435067</v>
+        <v>-0.1306607051435066</v>
       </c>
       <c r="R85" t="n">
         <v>0.1196435345551145</v>
@@ -12943,13 +12955,13 @@
         <v>-0.1123354443014818</v>
       </c>
       <c r="R86" t="n">
-        <v>-0.04051335372012838</v>
+        <v>-0.0405133537201283</v>
       </c>
       <c r="S86" t="n">
-        <v>-0.03457648132944026</v>
+        <v>-0.0345764813294402</v>
       </c>
       <c r="T86" t="n">
-        <v>-0.01563513989971912</v>
+        <v>-0.0156351398997191</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -13089,13 +13101,13 @@
         <v>-0.4737895295564234</v>
       </c>
       <c r="R87" t="n">
-        <v>0.09584392774808825</v>
+        <v>0.0958439277480882</v>
       </c>
       <c r="S87" t="n">
-        <v>0.02728843580169615</v>
+        <v>0.0272884358016961</v>
       </c>
       <c r="T87" t="n">
-        <v>-0.07713103353992135</v>
+        <v>-0.0771310335399213</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -13235,13 +13247,13 @@
         <v>-0.743714900294794</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.02643913548484633</v>
+        <v>-0.0264391354848463</v>
       </c>
       <c r="S88" t="n">
-        <v>0.01491913176775916</v>
+        <v>0.0149191317677591</v>
       </c>
       <c r="T88" t="n">
-        <v>0.08019645146493393</v>
+        <v>0.0801964514649339</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -13384,10 +13396,10 @@
         <v>-0.0237896889531391</v>
       </c>
       <c r="S89" t="n">
-        <v>-0.02015056001327488</v>
+        <v>-0.0201505600132748</v>
       </c>
       <c r="T89" t="n">
-        <v>-0.01893743788720503</v>
+        <v>-0.018937437887205</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -13527,13 +13539,13 @@
         <v>-0.4728125493370557</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01707051292762657</v>
+        <v>0.0170705129276265</v>
       </c>
       <c r="S90" t="n">
-        <v>-0.008125595359321447</v>
+        <v>-0.0081255953593214</v>
       </c>
       <c r="T90" t="n">
-        <v>-0.04579682607908009</v>
+        <v>-0.04579682607908</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -13667,19 +13679,19 @@
         <v>1.408547666134687</v>
       </c>
       <c r="P91" t="n">
-        <v>0.06031079270208295</v>
+        <v>0.0603107927020829</v>
       </c>
       <c r="Q91" t="n">
-        <v>-0.04279694478817513</v>
+        <v>-0.0427969447881751</v>
       </c>
       <c r="R91" t="n">
-        <v>0.1031077374902581</v>
+        <v>0.103107737490258</v>
       </c>
       <c r="S91" t="n">
         <v>0.1063850257404778</v>
       </c>
       <c r="T91" t="n">
-        <v>0.1495316370166237</v>
+        <v>0.1495316370166236</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -13819,13 +13831,13 @@
         <v>-0.5157658515448551</v>
       </c>
       <c r="R92" t="n">
-        <v>0.07312005209358485</v>
+        <v>0.0731200520935848</v>
       </c>
       <c r="S92" t="n">
-        <v>-0.00820024988032253</v>
+        <v>-0.0082002498803225</v>
       </c>
       <c r="T92" t="n">
-        <v>0.002874242309343744</v>
+        <v>0.0028742423093437</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -13965,13 +13977,13 @@
         <v>-0.3687022076974349</v>
       </c>
       <c r="R93" t="n">
-        <v>-0.05992403875488267</v>
+        <v>-0.0599240387548826</v>
       </c>
       <c r="S93" t="n">
-        <v>-0.05288275182624186</v>
+        <v>-0.0528827518262418</v>
       </c>
       <c r="T93" t="n">
-        <v>-0.02698991051106081</v>
+        <v>-0.0269899105110608</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -14224,7 +14236,7 @@
         <v>24.45000076293945</v>
       </c>
       <c r="G95" t="n">
-        <v>24.59500007629395</v>
+        <v>24.59500007629394</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
@@ -14251,16 +14263,16 @@
         <v>1.342068942918894</v>
       </c>
       <c r="P95" t="n">
-        <v>-0.05474978994614332</v>
+        <v>-0.0547497899461433</v>
       </c>
       <c r="Q95" t="n">
-        <v>-0.1191121758885341</v>
+        <v>-0.119112175888534</v>
       </c>
       <c r="R95" t="n">
-        <v>0.06436238594239073</v>
+        <v>0.0643623859423907</v>
       </c>
       <c r="S95" t="n">
-        <v>0.08234051890757801</v>
+        <v>0.082340518907578</v>
       </c>
       <c r="T95" t="n">
         <v>0.1061037370642961</v>
@@ -14403,13 +14415,13 @@
         <v>-0.6615022060536935</v>
       </c>
       <c r="R96" t="n">
-        <v>0.04815228090181711</v>
+        <v>0.0481522809018171</v>
       </c>
       <c r="S96" t="n">
-        <v>0.0001946720350322062</v>
+        <v>0.0001946720350322</v>
       </c>
       <c r="T96" t="n">
-        <v>-0.1072661761966756</v>
+        <v>-0.1072661761966755</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -14692,16 +14704,16 @@
         <v>-0.4693326259662189</v>
       </c>
       <c r="Q98" t="n">
-        <v>-0.4407415447034692</v>
+        <v>-0.4407415447034691</v>
       </c>
       <c r="R98" t="n">
-        <v>-0.02859108126274978</v>
+        <v>-0.0285910812627497</v>
       </c>
       <c r="S98" t="n">
-        <v>-0.03049073835550409</v>
+        <v>-0.030490738355504</v>
       </c>
       <c r="T98" t="n">
-        <v>-0.02975553039293743</v>
+        <v>-0.0297555303929374</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -14838,7 +14850,7 @@
         <v>-0.4990972135188372</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.348008371068298</v>
+        <v>0.3480083710682979</v>
       </c>
       <c r="R99" t="n">
         <v>-0.8471055845871351</v>
@@ -14993,7 +15005,7 @@
         <v>0.18967779672813</v>
       </c>
       <c r="T100" t="n">
-        <v>0.157234860136511</v>
+        <v>0.1572348601365109</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -15127,19 +15139,19 @@
         <v>1.263202639796775</v>
       </c>
       <c r="P101" t="n">
-        <v>0.2764584105717312</v>
+        <v>0.2764584105717311</v>
       </c>
       <c r="Q101" t="n">
         <v>0.3104349203868266</v>
       </c>
       <c r="R101" t="n">
-        <v>-0.03397650981509548</v>
+        <v>-0.0339765098150954</v>
       </c>
       <c r="S101" t="n">
-        <v>-0.01014455492987565</v>
+        <v>-0.0101445549298756</v>
       </c>
       <c r="T101" t="n">
-        <v>0.05463310839961222</v>
+        <v>0.0546331083996122</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -15246,7 +15258,7 @@
         <v>25.45000076293945</v>
       </c>
       <c r="G102" t="n">
-        <v>25.34500007629395</v>
+        <v>25.34500007629394</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -15276,16 +15288,16 @@
         <v>0.1707121487796357</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.1591224805118085</v>
+        <v>0.1591224805118084</v>
       </c>
       <c r="R102" t="n">
-        <v>0.01158966826782723</v>
+        <v>0.0115896682678272</v>
       </c>
       <c r="S102" t="n">
         <v>0.0171764069228808</v>
       </c>
       <c r="T102" t="n">
-        <v>0.01219919491019639</v>
+        <v>0.0121991949101963</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -15419,19 +15431,19 @@
         <v>1.237473806055042</v>
       </c>
       <c r="P103" t="n">
-        <v>0.01922610337012998</v>
+        <v>0.0192261033701299</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.005173869868034567</v>
+        <v>0.0051738698680345</v>
       </c>
       <c r="R103" t="n">
-        <v>0.01405223350209541</v>
+        <v>0.0140522335020954</v>
       </c>
       <c r="S103" t="n">
-        <v>-0.002638757207512808</v>
+        <v>-0.0026387572075128</v>
       </c>
       <c r="T103" t="n">
-        <v>-0.02907193540401273</v>
+        <v>-0.0290719354040127</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -15577,7 +15589,7 @@
         <v>-0.1395077610149973</v>
       </c>
       <c r="T104" t="n">
-        <v>-0.01798959408196454</v>
+        <v>-0.0179895940819645</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -15717,13 +15729,13 @@
         <v>-0.5815018965148691</v>
       </c>
       <c r="R105" t="n">
-        <v>0.000720587542581308</v>
+        <v>0.0007205875425812999</v>
       </c>
       <c r="S105" t="n">
-        <v>-0.02455030479634046</v>
+        <v>-0.0245503047963404</v>
       </c>
       <c r="T105" t="n">
-        <v>-0.04417307408505444</v>
+        <v>-0.0441730740850544</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -15863,7 +15875,7 @@
         <v>-0.3232757569286884</v>
       </c>
       <c r="R106" t="n">
-        <v>-0.08530183716053141</v>
+        <v>-0.0853018371605314</v>
       </c>
       <c r="S106" t="n">
         <v>-0.1043928856295968</v>
@@ -16000,22 +16012,22 @@
         <v>187965.075</v>
       </c>
       <c r="O107" t="n">
-        <v>0.9824689748708401</v>
+        <v>0.98246897487084</v>
       </c>
       <c r="P107" t="n">
-        <v>-0.09454941843869946</v>
+        <v>-0.09454941843869941</v>
       </c>
       <c r="Q107" t="n">
         <v>-0.1212234067730133</v>
       </c>
       <c r="R107" t="n">
-        <v>0.02667398833431388</v>
+        <v>0.0266739883343138</v>
       </c>
       <c r="S107" t="n">
-        <v>0.02905501884558828</v>
+        <v>0.0290550188455882</v>
       </c>
       <c r="T107" t="n">
-        <v>0.02210217752794122</v>
+        <v>0.0221021775279412</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -16146,7 +16158,7 @@
         <v>40160.625</v>
       </c>
       <c r="O108" t="n">
-        <v>0.9779115046249821</v>
+        <v>0.977911504624982</v>
       </c>
       <c r="P108" t="n">
         <v>-0.441286785851446</v>
@@ -16161,7 +16173,7 @@
         <v>0.1035884382351014</v>
       </c>
       <c r="T108" t="n">
-        <v>0.07736743790408696</v>
+        <v>0.0773674379040869</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -16301,13 +16313,13 @@
         <v>0.8948839590163155</v>
       </c>
       <c r="R109" t="n">
-        <v>-0.07128709944504064</v>
+        <v>-0.07128709944504059</v>
       </c>
       <c r="S109" t="n">
-        <v>0.03238110729627142</v>
+        <v>0.0323811072962714</v>
       </c>
       <c r="T109" t="n">
-        <v>0.2174316578102309</v>
+        <v>0.2174316578102308</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -16596,7 +16608,7 @@
         <v>-1.339939434261042</v>
       </c>
       <c r="S111" t="n">
-        <v>-0.9898732307566265</v>
+        <v>-0.9898732307566264</v>
       </c>
       <c r="T111" t="n">
         <v>-0.2736483963386789</v>
@@ -16852,7 +16864,7 @@
         <v>9.5</v>
       </c>
       <c r="G113" t="n">
-        <v>9.430000114440919</v>
+        <v>9.43000011444092</v>
       </c>
       <c r="H113" t="b">
         <v>1</v>
@@ -16879,19 +16891,19 @@
         <v>1.354523549746821</v>
       </c>
       <c r="P113" t="n">
-        <v>0.002306052593366914</v>
+        <v>0.0023060525933669</v>
       </c>
       <c r="Q113" t="n">
         <v>-0.0424829608481905</v>
       </c>
       <c r="R113" t="n">
-        <v>0.04478901344155742</v>
+        <v>0.0447890134415574</v>
       </c>
       <c r="S113" t="n">
-        <v>0.05111862856519004</v>
+        <v>0.05111862856519</v>
       </c>
       <c r="T113" t="n">
-        <v>0.04957722191631726</v>
+        <v>0.0495772219163172</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -17031,10 +17043,10 @@
         <v>0.5752795574138145</v>
       </c>
       <c r="R114" t="n">
-        <v>0.004936610062827862</v>
+        <v>0.0049366100628278</v>
       </c>
       <c r="S114" t="n">
-        <v>0.02642087228851897</v>
+        <v>0.0264208722885189</v>
       </c>
       <c r="T114" t="n">
         <v>0.1265021754495792</v>
@@ -17320,16 +17332,16 @@
         <v>-0.309748190721681</v>
       </c>
       <c r="Q116" t="n">
-        <v>-0.293916409985769</v>
+        <v>-0.2939164099857689</v>
       </c>
       <c r="R116" t="n">
-        <v>-0.01583178073591207</v>
+        <v>-0.015831780735912</v>
       </c>
       <c r="S116" t="n">
-        <v>-0.03729606517484407</v>
+        <v>-0.037296065174844</v>
       </c>
       <c r="T116" t="n">
-        <v>-0.04384085346549482</v>
+        <v>-0.0438408534654948</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -17445,7 +17457,7 @@
         <v>50.39162483234158</v>
       </c>
       <c r="J117" t="n">
-        <v>51.89844585490204</v>
+        <v>51.89844585490203</v>
       </c>
       <c r="K117" t="n">
         <v>51.0123427848267</v>
@@ -17463,10 +17475,10 @@
         <v>1.374928472017238</v>
       </c>
       <c r="P117" t="n">
-        <v>0.08156098575179627</v>
+        <v>0.0815609857517962</v>
       </c>
       <c r="Q117" t="n">
-        <v>-0.138800461182581</v>
+        <v>-0.1388004611825809</v>
       </c>
       <c r="R117" t="n">
         <v>0.2203614469343772</v>
@@ -17525,7 +17537,7 @@
         <v>-5</v>
       </c>
       <c r="AF117" t="n">
-        <v>-93.30000000000001</v>
+        <v>-93.3</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -17615,10 +17627,10 @@
         <v>-0.2020503495802263</v>
       </c>
       <c r="R118" t="n">
-        <v>0.03606156835212854</v>
+        <v>0.0360615683521285</v>
       </c>
       <c r="S118" t="n">
-        <v>0.06991265137774288</v>
+        <v>0.0699126513777428</v>
       </c>
       <c r="T118" t="n">
         <v>0.1262341542874416</v>
@@ -17764,10 +17776,10 @@
         <v>0.2126408975401602</v>
       </c>
       <c r="S119" t="n">
-        <v>0.2490948387569815</v>
+        <v>0.2490948387569814</v>
       </c>
       <c r="T119" t="n">
-        <v>0.3096065989534597</v>
+        <v>0.3096065989534596</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>

--- a/output/screening_result.xlsx
+++ b/output/screening_result.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,202 +417,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>candidate_level</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>candidate_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MA20</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>是否站上 MA20</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>K 值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>D 值</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Volume_MA5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Volume_MA20</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Volume_MA40</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>放量倍數</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>MACD_DIF</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>MACD_Signal</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>MACD_Histogram</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前1日</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前2日</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MACD_綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>是否符合 KD 區間</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>是否符合 RSI 區間</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>是否明顯放量</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>MACD 是否綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>法人近 5 日是否合計買超</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>投信近 5 日是否買超</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>外資近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>投信近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>自營商近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>三大法人近 1 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>外資近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>投信近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>自營商近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>三大法人近 5 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>外資近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>投信近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>自營商近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>三大法人近 20 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
         </is>
@@ -658,7 +646,7 @@
         <v>26.25</v>
       </c>
       <c r="G2" t="n">
-        <v>26.08249998092651</v>
+        <v>26.08249998092652</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -1969,7 +1957,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30.14999961853027</v>
+        <v>30.14999961853028</v>
       </c>
       <c r="G11" t="n">
         <v>29.92999982833862</v>
@@ -2115,10 +2103,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20.14999961853027</v>
+        <v>20.14999961853028</v>
       </c>
       <c r="G12" t="n">
-        <v>19.89499998092651</v>
+        <v>19.89499998092652</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -2276,7 +2264,7 @@
         <v>35.66039521645349</v>
       </c>
       <c r="K13" t="n">
-        <v>47.34339692506855</v>
+        <v>47.34339692506856</v>
       </c>
       <c r="L13" t="n">
         <v>16672</v>
@@ -6942,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>39.98814663129379</v>
+        <v>39.9881466312938</v>
       </c>
       <c r="J45" t="n">
         <v>42.8935006568544</v>
@@ -8396,7 +8384,7 @@
         <v>52.29999923706055</v>
       </c>
       <c r="G55" t="n">
-        <v>53.40000019073486</v>
+        <v>53.40000019073487</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
@@ -8688,7 +8676,7 @@
         <v>39.04999923706055</v>
       </c>
       <c r="G57" t="n">
-        <v>37.96499996185302</v>
+        <v>37.96499996185303</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -8977,7 +8965,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>20.64999961853027</v>
+        <v>20.64999961853028</v>
       </c>
       <c r="G59" t="n">
         <v>23.79750022888184</v>
@@ -9284,7 +9272,7 @@
         <v>48.28841768086394</v>
       </c>
       <c r="K61" t="n">
-        <v>51.41556301083143</v>
+        <v>51.41556301083144</v>
       </c>
       <c r="L61" t="n">
         <v>272996</v>
@@ -10389,7 +10377,7 @@
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>-4.415999999999999</v>
+        <v>-4.416</v>
       </c>
       <c r="AI68" t="n">
         <v>289.343</v>
@@ -13944,7 +13932,7 @@
         <v>25.04999923706055</v>
       </c>
       <c r="G93" t="n">
-        <v>25.97499980926514</v>
+        <v>25.97499980926513</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
@@ -15109,7 +15097,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>20.64999961853027</v>
+        <v>20.64999961853028</v>
       </c>
       <c r="G101" t="n">
         <v>20.59749975204468</v>
@@ -15121,7 +15109,7 @@
         <v>35.00645363422731</v>
       </c>
       <c r="J101" t="n">
-        <v>49.13598453200559</v>
+        <v>49.1359845320056</v>
       </c>
       <c r="K101" t="n">
         <v>51.79629158174377</v>
@@ -16724,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>29.33932229205367</v>
+        <v>29.33932229205368</v>
       </c>
       <c r="J112" t="n">
         <v>42.62673381669126</v>
@@ -17591,7 +17579,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>28.39999961853027</v>
+        <v>28.39999961853028</v>
       </c>
       <c r="G118" t="n">
         <v>28.71999988555908</v>

--- a/output/screening_result.xlsx
+++ b/output/screening_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金穎生技</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>31.85000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>33.37750024795533</v>
+        <v>32.76749982833862</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>46.16326521060081</v>
+        <v>34.20116889257829</v>
       </c>
       <c r="J2" t="n">
-        <v>48.58313318446378</v>
+        <v>46.7549271938021</v>
       </c>
       <c r="K2" t="n">
-        <v>45.19867833803188</v>
+        <v>30.97104170868637</v>
       </c>
       <c r="L2" t="n">
-        <v>82471.2</v>
+        <v>58835.8</v>
       </c>
       <c r="M2" t="n">
-        <v>30767.85</v>
+        <v>34890.6</v>
       </c>
       <c r="N2" t="n">
-        <v>27940.825</v>
+        <v>44255.875</v>
       </c>
       <c r="O2" t="n">
-        <v>2.680434284488516</v>
+        <v>1.686293729543201</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2953300337523359</v>
+        <v>-0.2842236917777115</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6025421697441639</v>
+        <v>-0.2472639884589217</v>
       </c>
       <c r="R2" t="n">
-        <v>0.307212135991828</v>
+        <v>-0.03695970331878973</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4401988148427923</v>
+        <v>0.007712216259010862</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4828921628240106</v>
+        <v>0.03598331456728865</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,23 +744,23 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>18.506</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>22.506</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>醫影</t>
+          <t>金穎生技</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>64.69999694824219</v>
+        <v>32.5</v>
       </c>
       <c r="G3" t="n">
-        <v>63.84499969482422</v>
+        <v>33.30500020980835</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.56531169597832</v>
+        <v>37.67206186357402</v>
       </c>
       <c r="J3" t="n">
-        <v>48.8700147194887</v>
+        <v>44.94610939283048</v>
       </c>
       <c r="K3" t="n">
-        <v>49.84828897352286</v>
+        <v>44.71576286720469</v>
       </c>
       <c r="L3" t="n">
-        <v>206783</v>
+        <v>75217.39999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>84803.25</v>
+        <v>31204.4</v>
       </c>
       <c r="N3" t="n">
-        <v>62560.525</v>
+        <v>28084.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.438385321317285</v>
+        <v>2.410474163899963</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.08841321408539216</v>
+        <v>-0.3693563248643272</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5605607697223153</v>
+        <v>-0.547673755025359</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4721475556369231</v>
+        <v>0.1783174301610317</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5691148767760413</v>
+        <v>0.3039546998325752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5537296955733102</v>
+        <v>0.4366870868234886</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>醫影</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>63.70000076293945</v>
       </c>
       <c r="G4" t="n">
-        <v>40.86250038146973</v>
+        <v>63.83499965667725</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>42.75388237561103</v>
+        <v>39.75618934471713</v>
       </c>
       <c r="J4" t="n">
-        <v>48.31327520124016</v>
+        <v>45.83207292789818</v>
       </c>
       <c r="K4" t="n">
-        <v>46.11145033935261</v>
+        <v>46.48751437902355</v>
       </c>
       <c r="L4" t="n">
-        <v>1165975.2</v>
+        <v>208260.4</v>
       </c>
       <c r="M4" t="n">
-        <v>565816.8</v>
+        <v>88873.2</v>
       </c>
       <c r="N4" t="n">
-        <v>515385.175</v>
+        <v>64420.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.060693850023541</v>
+        <v>2.34334310005716</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2942000323273888</v>
+        <v>-0.1477754006326819</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0169598560862944</v>
+        <v>-0.4743453567101243</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2772401762410944</v>
+        <v>0.3265699560774424</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5272560233138188</v>
+        <v>0.4706998031646441</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4348084683837315</v>
+        <v>0.567554105459778</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>冠好</t>
+          <t>陽程</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16.35000038146973</v>
+        <v>119.5</v>
       </c>
       <c r="G5" t="n">
-        <v>16.59499998092651</v>
+        <v>121.35</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>35.62920542548411</v>
+        <v>41.83528876317562</v>
       </c>
       <c r="J5" t="n">
-        <v>46.87704150003889</v>
+        <v>47.88888800262654</v>
       </c>
       <c r="K5" t="n">
-        <v>44.78333336420408</v>
+        <v>45.89904698100938</v>
       </c>
       <c r="L5" t="n">
-        <v>363227.6</v>
+        <v>3994168.2</v>
       </c>
       <c r="M5" t="n">
-        <v>195295.85</v>
+        <v>1955082.1</v>
       </c>
       <c r="N5" t="n">
-        <v>194461.05</v>
+        <v>1880916.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.859883863379585</v>
+        <v>2.042966993560015</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09697878085917822</v>
+        <v>-0.02961160800350626</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08804980493502867</v>
+        <v>-0.6120302320882816</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00892897592414954</v>
+        <v>0.5824186240847753</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06135892317641378</v>
+        <v>1.122055107980383</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09790119430808275</v>
+        <v>0.7292870329916203</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,78 +1198,78 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>接近</t>
+          <t>符合</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>建碁</t>
+          <t>謚源</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>54.29999923706055</v>
+        <v>28.5</v>
       </c>
       <c r="G6" t="n">
-        <v>54.38999996185303</v>
+        <v>30.10249986648559</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>58.96574580230311</v>
+        <v>32.36196866560461</v>
       </c>
       <c r="J6" t="n">
-        <v>55.52595083685556</v>
+        <v>31.65241255163256</v>
       </c>
       <c r="K6" t="n">
-        <v>49.46005100914449</v>
+        <v>34.19746995871115</v>
       </c>
       <c r="L6" t="n">
-        <v>1820109.6</v>
+        <v>21449</v>
       </c>
       <c r="M6" t="n">
-        <v>728900.3</v>
+        <v>11115</v>
       </c>
       <c r="N6" t="n">
-        <v>853447.775</v>
+        <v>13354.425</v>
       </c>
       <c r="O6" t="n">
-        <v>2.497062492634452</v>
+        <v>1.929734592892488</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.03844058398463801</v>
+        <v>-0.1851556401382162</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2336324275600637</v>
+        <v>-0.1412927157493716</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1951918435754257</v>
+        <v>-0.04386292438884462</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2570925932206787</v>
+        <v>0.07983922536489227</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2060946556894083</v>
+        <v>0.02805498769514908</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,44 +1307,44 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.413</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-2.587</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>631.6129999999999</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>10.905</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>642.5179999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-125.4910000000001</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-194.502</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-319.9930000000001</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,58 +1373,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>161</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="G7" t="n">
-        <v>163.125</v>
+        <v>3.272500002384186</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>48.74764341013729</v>
+        <v>39.83555751077201</v>
       </c>
       <c r="J7" t="n">
-        <v>57.47045056803849</v>
+        <v>42.94215193331156</v>
       </c>
       <c r="K7" t="n">
-        <v>49.12023369651146</v>
+        <v>48.30974711621549</v>
       </c>
       <c r="L7" t="n">
-        <v>1645613.6</v>
+        <v>38200</v>
       </c>
       <c r="M7" t="n">
-        <v>747688.15</v>
+        <v>25180.25</v>
       </c>
       <c r="N7" t="n">
-        <v>863011.925</v>
+        <v>70565.125</v>
       </c>
       <c r="O7" t="n">
-        <v>2.200935777837324</v>
+        <v>1.517061983101836</v>
       </c>
       <c r="P7" t="n">
-        <v>2.809350823157502</v>
+        <v>-0.02833480713405523</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.852012578426099</v>
+        <v>0.008157566339477909</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.04266175526859728</v>
+        <v>-0.03649237347353314</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5820503242739714</v>
+        <v>-0.04527943442210391</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7757032528995449</v>
+        <v>-0.05067223432556733</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.135</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>101.135</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>758.664</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>49.61799999999999</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>807.2819999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>931.7889999999998</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>50.94499999999999</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>980.7340000000002</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1505,63 +1505,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>237</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>35.08249988555908</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>42.88556258016536</v>
+        <v>43.88879848256521</v>
       </c>
       <c r="J8" t="n">
-        <v>46.98097560738728</v>
+        <v>34.26514633615096</v>
       </c>
       <c r="K8" t="n">
-        <v>47.83649861854428</v>
+        <v>55.01425153996799</v>
       </c>
       <c r="L8" t="n">
-        <v>11952299.4</v>
+        <v>234643</v>
       </c>
       <c r="M8" t="n">
-        <v>7073758.75</v>
+        <v>79511.3</v>
       </c>
       <c r="N8" t="n">
-        <v>10460166.875</v>
+        <v>65380.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.689667378039999</v>
+        <v>2.951064817202083</v>
       </c>
       <c r="P8" t="n">
-        <v>5.664737297711383</v>
+        <v>-0.1093109768636467</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.627210990566164</v>
+        <v>-0.282460226879769</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.962473692854781</v>
+        <v>0.1731492500161223</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7760320829832921</v>
+        <v>0.1005374438711487</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7690187135846802</v>
+        <v>-0.125891234117313</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1599,44 +1599,44 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1665,49 +1665,49 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11.89999961853027</v>
+        <v>10.05000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>12.39499998092651</v>
+        <v>10.17850003242493</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>32.40083937704979</v>
+        <v>22.68322382825935</v>
       </c>
       <c r="J9" t="n">
-        <v>39.44386926923148</v>
+        <v>27.40751533282922</v>
       </c>
       <c r="K9" t="n">
-        <v>23.01765585904785</v>
+        <v>48.27429996590129</v>
       </c>
       <c r="L9" t="n">
-        <v>1040327.4</v>
+        <v>54000</v>
       </c>
       <c r="M9" t="n">
-        <v>619394.05</v>
+        <v>21856.85</v>
       </c>
       <c r="N9" t="n">
-        <v>586327.775</v>
+        <v>38079.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.679588946648745</v>
+        <v>2.470621338390482</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1644803557939039</v>
+        <v>-0.01444919142518941</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.139553014303872</v>
+        <v>0.009160539967731474</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.02492734149003187</v>
+        <v>-0.02360973139292089</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.006472474653629268</v>
+        <v>-0.02615463652838756</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.005093496047613277</v>
+        <v>-0.0201010893121259</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-355.015</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1754,35 +1754,35 @@
         <v>-1</v>
       </c>
       <c r="AE9" t="n">
-        <v>-356.015</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>329.439</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="AI9" t="n">
-        <v>323.439</v>
+        <v>6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1026.431</v>
+        <v>33.8</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="AM9" t="n">
-        <v>1017.431</v>
+        <v>35.8</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>高興昌</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1811,49 +1811,49 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>29.29999923706055</v>
+        <v>83.80000305175781</v>
       </c>
       <c r="G10" t="n">
-        <v>30.44499969482422</v>
+        <v>81.81000061035157</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>22.25069660727758</v>
+        <v>67.48525432181248</v>
       </c>
       <c r="J10" t="n">
-        <v>30.12380561816843</v>
+        <v>67.97897101414067</v>
       </c>
       <c r="K10" t="n">
-        <v>42.01514213093559</v>
+        <v>48.11209203671847</v>
       </c>
       <c r="L10" t="n">
-        <v>55250.4</v>
+        <v>60671.2</v>
       </c>
       <c r="M10" t="n">
-        <v>33735.35</v>
+        <v>32179.2</v>
       </c>
       <c r="N10" t="n">
-        <v>35331.7</v>
+        <v>40216.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.637759797956743</v>
+        <v>1.885416666666667</v>
       </c>
       <c r="P10" t="n">
-        <v>0.08589856619916247</v>
+        <v>-0.6153611180446887</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3189821658729638</v>
+        <v>-1.821850428130239</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.2330835996738013</v>
+        <v>1.20648931008555</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2084710526658777</v>
+        <v>1.476029619625301</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2132545257407206</v>
+        <v>1.396051668012197</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1891,44 +1891,44 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>0.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>4</v>
+        <v>-4.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.012</v>
+        <v>1.075</v>
       </c>
       <c r="AI10" t="n">
-        <v>20.012</v>
+        <v>21.075</v>
       </c>
       <c r="AJ10" t="n">
-        <v>101.8</v>
+        <v>24.797</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.013</v>
+        <v>0.9149999999999997</v>
       </c>
       <c r="AM10" t="n">
-        <v>105.813</v>
+        <v>25.712</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1943,63 +1943,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>大世科</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25.79999923706055</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>27.52999992370605</v>
+        <v>58.99000015258789</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>24.77521016558149</v>
+        <v>37.65263740402298</v>
       </c>
       <c r="J11" t="n">
-        <v>39.36393242577476</v>
+        <v>41.93440379910899</v>
       </c>
       <c r="K11" t="n">
-        <v>48.04070718458959</v>
+        <v>41.64448689393967</v>
       </c>
       <c r="L11" t="n">
-        <v>84857786.59999999</v>
+        <v>331052.4</v>
       </c>
       <c r="M11" t="n">
-        <v>52429682.35</v>
+        <v>180899.1</v>
       </c>
       <c r="N11" t="n">
-        <v>36681060.425</v>
+        <v>272971.475</v>
       </c>
       <c r="O11" t="n">
-        <v>1.618506593908441</v>
+        <v>1.830038955417689</v>
       </c>
       <c r="P11" t="n">
-        <v>1.083040072872503</v>
+        <v>-0.6291810146961936</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55755226088889</v>
+        <v>-0.7967228055718107</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.4745121880163867</v>
+        <v>0.1675417908756172</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3238642471900397</v>
+        <v>0.2637958927565475</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1571699181305566</v>
+        <v>0.2751363874559156</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2033,48 +2033,48 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>-8484.144</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>-100.97</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-8575.114</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-19520.58</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1652</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1547.499</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-19416.079</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-39828.72100000001</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1995</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2819.464</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-40653.185</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>美時</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2103,49 +2103,49 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>196.5</v>
+        <v>14.5</v>
       </c>
       <c r="G12" t="n">
-        <v>195.425</v>
+        <v>13.78499999046326</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>52.87133625196203</v>
+        <v>37.57267046981925</v>
       </c>
       <c r="J12" t="n">
-        <v>61.54086074583934</v>
+        <v>37.60461473589337</v>
       </c>
       <c r="K12" t="n">
-        <v>47.61987644017369</v>
+        <v>68.92595875800271</v>
       </c>
       <c r="L12" t="n">
-        <v>3387909.8</v>
+        <v>634708.2</v>
       </c>
       <c r="M12" t="n">
-        <v>2120034.5</v>
+        <v>359733.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2118553.95</v>
+        <v>364984.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.598044654461991</v>
+        <v>1.764382506069069</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9985097448418117</v>
+        <v>0.2079493987880063</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.5189336234849583</v>
+        <v>0.2040356100310344</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51744336832677</v>
+        <v>0.003913788756971903</v>
       </c>
       <c r="S12" t="n">
-        <v>2.274373587824656</v>
+        <v>-0.04397165581430373</v>
       </c>
       <c r="T12" t="n">
-        <v>2.541230748359202</v>
+        <v>-0.03819207047870121</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2174,53 +2174,53 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>-451.119</v>
+        <v>66</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>-123.525</v>
+        <v>11.116</v>
       </c>
       <c r="AE12" t="n">
-        <v>-572.644</v>
+        <v>77.116</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1611.115</v>
+        <v>-6</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-188.534</v>
+        <v>14.116</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1777.649</v>
+        <v>8.116</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-1491.998</v>
+        <v>279.9730000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>-51.281</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-22.996</v>
+        <v>18.118</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1566.274999999999</v>
+        <v>298.0910000000001</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>鑫傳</t>
+          <t>琉園</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2249,58 +2249,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="G13" t="n">
-        <v>44.925</v>
+        <v>26.63749980926514</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>37.2657380842941</v>
+        <v>38.62553062702429</v>
       </c>
       <c r="J13" t="n">
-        <v>40.22400382333809</v>
+        <v>53.07618117697966</v>
       </c>
       <c r="K13" t="n">
-        <v>33.74670619381261</v>
+        <v>46.39700251663071</v>
       </c>
       <c r="L13" t="n">
-        <v>36902.2</v>
+        <v>874825.8</v>
       </c>
       <c r="M13" t="n">
-        <v>32700.7</v>
+        <v>259675.35</v>
       </c>
       <c r="N13" t="n">
-        <v>20178.4</v>
+        <v>147102.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.128483488121049</v>
+        <v>3.36892123183814</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.459662360254832</v>
+        <v>0.7588719716173138</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.414517732762908</v>
+        <v>0.767595528431706</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.04514462749192427</v>
+        <v>-0.008723556814392186</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06143745685303448</v>
+        <v>0.1983907606392513</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1026103070189184</v>
+        <v>0.4246791737939484</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -2377,76 +2377,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>鄉林</t>
+          <t>億而得</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.949999809265137</v>
+        <v>73.59999847412109</v>
       </c>
       <c r="G14" t="n">
-        <v>8.02900002002716</v>
+        <v>82.3799991607666</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>32.92880611702692</v>
+        <v>33.60539440765977</v>
       </c>
       <c r="J14" t="n">
-        <v>33.77507897722676</v>
+        <v>50.38770062145136</v>
       </c>
       <c r="K14" t="n">
-        <v>46.50552120989041</v>
+        <v>34.47557410027768</v>
       </c>
       <c r="L14" t="n">
-        <v>402955</v>
+        <v>384565.8</v>
       </c>
       <c r="M14" t="n">
-        <v>487324.1</v>
+        <v>226978.6</v>
       </c>
       <c r="N14" t="n">
-        <v>655056.05</v>
+        <v>201913.325</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8268727116101995</v>
+        <v>1.694282192241912</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.03402668222836791</v>
+        <v>-2.288830326104119</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.02996669685491522</v>
+        <v>-2.471405681191704</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.004059985373452694</v>
+        <v>0.1825753550875855</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.004788887023853945</v>
+        <v>0.9365995686792781</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.005130175734831665</v>
+        <v>1.425888930272709</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2475,44 +2475,44 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>-67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>37.15899999999989</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>31.15899999999988</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>泰偉</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2541,49 +2541,49 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>19.20000076293945</v>
+        <v>19.04999923706055</v>
       </c>
       <c r="G15" t="n">
-        <v>19.46000013351441</v>
+        <v>18.88000020980835</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>29.5039183931719</v>
+        <v>28.98792842759279</v>
       </c>
       <c r="J15" t="n">
-        <v>46.96913910844508</v>
+        <v>25.85435993354733</v>
       </c>
       <c r="K15" t="n">
-        <v>46.95095878350291</v>
+        <v>49.99304505721955</v>
       </c>
       <c r="L15" t="n">
-        <v>6719.4</v>
+        <v>552712.8</v>
       </c>
       <c r="M15" t="n">
-        <v>2809.3</v>
+        <v>332138.85</v>
       </c>
       <c r="N15" t="n">
-        <v>3679.9</v>
+        <v>341285.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.391841383974656</v>
+        <v>1.664101624967992</v>
       </c>
       <c r="P15" t="n">
-        <v>0.08707533621713281</v>
+        <v>-0.3692426839056857</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.138797006313626</v>
+        <v>-0.4259374334402445</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.0517216700964932</v>
+        <v>0.05669474953455877</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0287885626551099</v>
+        <v>0.008678643819726106</v>
       </c>
       <c r="T15" t="n">
-        <v>0.008000994201703554</v>
+        <v>0.02429219497772495</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -2673,63 +2673,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>矽瑪</t>
+          <t>隴華</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>23.85000038146973</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="G16" t="n">
-        <v>24.91000003814697</v>
+        <v>10.24949994087219</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>29.36006022736021</v>
+        <v>28.18173109760893</v>
       </c>
       <c r="J16" t="n">
-        <v>42.88937426397032</v>
+        <v>34.21639310751981</v>
       </c>
       <c r="K16" t="n">
-        <v>47.04168525708328</v>
+        <v>34.46499097567447</v>
       </c>
       <c r="L16" t="n">
-        <v>3901215.2</v>
+        <v>182849.4</v>
       </c>
       <c r="M16" t="n">
-        <v>1729662.8</v>
+        <v>119690.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1333031.625</v>
+        <v>145805.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.255477310375178</v>
+        <v>1.527680049193381</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952452325148911</v>
+        <v>-1.029391197859482</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7366469021468128</v>
+        <v>-1.227866872757534</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.1414016696319217</v>
+        <v>0.1984756748980518</v>
       </c>
       <c r="S16" t="n">
-        <v>0.004176689247279763</v>
+        <v>0.2482502348523425</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0924984099369125</v>
+        <v>0.2827185032452117</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2776,35 +2776,35 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>鐿鈦</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2833,49 +2833,49 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>126</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="G17" t="n">
-        <v>124.575</v>
+        <v>71.53499984741211</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>33.58077565196341</v>
+        <v>40.39558161920169</v>
       </c>
       <c r="J17" t="n">
-        <v>44.61004627137724</v>
+        <v>35.88024064757597</v>
       </c>
       <c r="K17" t="n">
-        <v>52.58391192332774</v>
+        <v>50.8246034843458</v>
       </c>
       <c r="L17" t="n">
-        <v>485072.4</v>
+        <v>105811.6</v>
       </c>
       <c r="M17" t="n">
-        <v>238323.95</v>
+        <v>69813.05</v>
       </c>
       <c r="N17" t="n">
-        <v>275188.675</v>
+        <v>75571.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.035348944157731</v>
+        <v>1.515642132810413</v>
       </c>
       <c r="P17" t="n">
-        <v>3.488579158735391</v>
+        <v>0.02389425982818238</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.657330827342911</v>
+        <v>-0.126289901993333</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.1687516686075208</v>
+        <v>0.1501841618215154</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1797863825875132</v>
+        <v>0.1837443075009714</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5142878668941568</v>
+        <v>-0.1931518098964864</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -2965,63 +2965,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>三星</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>69.30000305175781</v>
+        <v>55.90000152587891</v>
       </c>
       <c r="G18" t="n">
-        <v>72.01999969482422</v>
+        <v>55.97000026702881</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>29.87338712162247</v>
+        <v>31.46885293462732</v>
       </c>
       <c r="J18" t="n">
-        <v>45.10233595113262</v>
+        <v>27.82872676434698</v>
       </c>
       <c r="K18" t="n">
-        <v>37.51704438510552</v>
+        <v>45.19850266940327</v>
       </c>
       <c r="L18" t="n">
-        <v>17456.6</v>
+        <v>47446</v>
       </c>
       <c r="M18" t="n">
-        <v>9620</v>
+        <v>31478.95</v>
       </c>
       <c r="N18" t="n">
-        <v>10498.325</v>
+        <v>46414.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.814615384615385</v>
+        <v>1.507229434272744</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2014443984700023</v>
+        <v>-0.2643640459862695</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1455066001227262</v>
+        <v>-0.3015713415459557</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.3469509985927285</v>
+        <v>0.03720729555968616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2411634889835449</v>
+        <v>0.02293683951390135</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1879555585748414</v>
+        <v>0.01295446442208464</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3059,44 +3059,44 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>157.957</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>158.957</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>207.258</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>206.258</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3125,49 +3125,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="G19" t="n">
-        <v>199.9772712707519</v>
+        <v>116.2</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>28.83969087871156</v>
+        <v>20.45381637477141</v>
       </c>
       <c r="J19" t="n">
-        <v>45.85606606352801</v>
+        <v>21.05332618774105</v>
       </c>
       <c r="K19" t="n">
-        <v>33.76961041966187</v>
+        <v>31.6340594965926</v>
       </c>
       <c r="L19" t="n">
-        <v>328223.6</v>
+        <v>22646112.6</v>
       </c>
       <c r="M19" t="n">
-        <v>182503.8</v>
+        <v>15129263.05</v>
       </c>
       <c r="N19" t="n">
-        <v>192515.85</v>
+        <v>15397070.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.798448032314944</v>
+        <v>1.49684175132377</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.470882399588874</v>
+        <v>-1.651372612345611</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9877445820461588</v>
+        <v>-0.3744124110647332</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.483137817542715</v>
+        <v>-1.276960201280878</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3964979413355929</v>
+        <v>-1.317489393352069</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1065949271998299</v>
+        <v>-1.322068438919912</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3196,53 +3196,53 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>-277.7</v>
+        <v>7364.225</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>667.867</v>
       </c>
       <c r="AD19" t="n">
-        <v>-9.961</v>
+        <v>1471.702</v>
       </c>
       <c r="AE19" t="n">
-        <v>-287.661</v>
+        <v>9503.794</v>
       </c>
       <c r="AF19" t="n">
-        <v>-874.0889999999999</v>
+        <v>25203.23300000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>-1</v>
+        <v>6609.432999999999</v>
       </c>
       <c r="AH19" t="n">
-        <v>-44.064</v>
+        <v>-230.0959999999999</v>
       </c>
       <c r="AI19" t="n">
-        <v>-919.1529999999999</v>
+        <v>31582.56999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-623.4219999999999</v>
+        <v>-10658.216</v>
       </c>
       <c r="AK19" t="n">
-        <v>-4</v>
+        <v>39860.505</v>
       </c>
       <c r="AL19" t="n">
-        <v>-15.608</v>
+        <v>1102.389</v>
       </c>
       <c r="AM19" t="n">
-        <v>-643.03</v>
+        <v>30304.678</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3271,49 +3271,49 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>32.29999923706055</v>
+        <v>63.70000076293945</v>
       </c>
       <c r="G20" t="n">
-        <v>32.86249980926514</v>
+        <v>66.57499961853027</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>47.96840728804074</v>
+        <v>37.05669907100165</v>
       </c>
       <c r="J20" t="n">
-        <v>53.03180631014538</v>
+        <v>45.85657453889542</v>
       </c>
       <c r="K20" t="n">
-        <v>36.68521892464995</v>
+        <v>44.79795596157779</v>
       </c>
       <c r="L20" t="n">
-        <v>52398.4</v>
+        <v>53422664.2</v>
       </c>
       <c r="M20" t="n">
-        <v>32481.25</v>
+        <v>36302274.05</v>
       </c>
       <c r="N20" t="n">
-        <v>43401.225</v>
+        <v>74967714.15000001</v>
       </c>
       <c r="O20" t="n">
-        <v>1.613189147585145</v>
+        <v>1.471606548020096</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2303118463702134</v>
+        <v>0.4464598078507862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2380240626292243</v>
+        <v>0.9472419866448643</v>
       </c>
       <c r="R20" t="n">
-        <v>0.007712216259010862</v>
+        <v>-0.500782178794078</v>
       </c>
       <c r="S20" t="n">
-        <v>0.03598331456728865</v>
+        <v>-0.302490773193939</v>
       </c>
       <c r="T20" t="n">
-        <v>0.04593266921300102</v>
+        <v>-0.07824350527876467</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3342,53 +3342,53 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>-7</v>
+        <v>-4419.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4289.736</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>840.726</v>
       </c>
       <c r="AE20" t="n">
-        <v>-7</v>
+        <v>711.0120000000001</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>-39841.055</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>19709.309</v>
       </c>
       <c r="AH20" t="n">
-        <v>-2</v>
+        <v>599.682</v>
       </c>
       <c r="AI20" t="n">
-        <v>22</v>
+        <v>-19532.064</v>
       </c>
       <c r="AJ20" t="n">
-        <v>16.506</v>
+        <v>-73259.255</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>47614.03999999999</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>3896.301</v>
       </c>
       <c r="AM20" t="n">
-        <v>22.506</v>
+        <v>-21748.914</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3403,63 +3403,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9.970000267028809</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="G21" t="n">
-        <v>10.19100003242493</v>
+        <v>40.70250034332275</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>23.65897357211196</v>
+        <v>32.39430147742804</v>
       </c>
       <c r="J21" t="n">
-        <v>29.76966105051617</v>
+        <v>43.00695062211579</v>
       </c>
       <c r="K21" t="n">
-        <v>46.52241516716224</v>
+        <v>41.59021632757565</v>
       </c>
       <c r="L21" t="n">
-        <v>55400</v>
+        <v>839854</v>
       </c>
       <c r="M21" t="n">
-        <v>34856.85</v>
+        <v>581445.55</v>
       </c>
       <c r="N21" t="n">
-        <v>46929.25</v>
+        <v>527246.775</v>
       </c>
       <c r="O21" t="n">
-        <v>1.589357615504557</v>
+        <v>1.444424159751502</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.009138438963052664</v>
+        <v>0.008573556890979717</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.01792103940882016</v>
+        <v>0.01894093544148001</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.02705947837187283</v>
+        <v>-0.01036737855050029</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.02107656766364398</v>
+        <v>0.2757924237688137</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.01827285264647019</v>
+        <v>0.5256952519975534</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3518,23 +3518,23 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>37.8</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>45.8</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>海灣</t>
+          <t>中天</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3563,49 +3563,49 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17.5</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>17.66750020980835</v>
+        <v>16.04999990463257</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>26.49672157474144</v>
+        <v>30.2018799165296</v>
       </c>
       <c r="J22" t="n">
-        <v>25.6384242682923</v>
+        <v>46.72914865134435</v>
       </c>
       <c r="K22" t="n">
-        <v>41.34620022221119</v>
+        <v>47.20932299580701</v>
       </c>
       <c r="L22" t="n">
-        <v>37600.6</v>
+        <v>5148335.2</v>
       </c>
       <c r="M22" t="n">
-        <v>23839.85</v>
+        <v>4215930.7</v>
       </c>
       <c r="N22" t="n">
-        <v>25055.375</v>
+        <v>2975898.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.577216299599201</v>
+        <v>1.221162197945996</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.111098267052963</v>
+        <v>0.4247469504033461</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1351520342454886</v>
+        <v>0.4543180385261696</v>
       </c>
       <c r="R22" t="n">
-        <v>0.02405376719252558</v>
+        <v>-0.0295710881228235</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0391777525053868</v>
+        <v>0.0782007278445227</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0417203008336173</v>
+        <v>0.1910713809848755</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3709,49 +3709,49 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>109.5</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>116.725</v>
+        <v>14.18000001907349</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>19.9664388472977</v>
+        <v>33.9386509474139</v>
       </c>
       <c r="J23" t="n">
-        <v>21.35308108351696</v>
+        <v>46.73664450329568</v>
       </c>
       <c r="K23" t="n">
-        <v>32.60699649988233</v>
+        <v>48.42685200365179</v>
       </c>
       <c r="L23" t="n">
-        <v>21591870.4</v>
+        <v>2203071</v>
       </c>
       <c r="M23" t="n">
-        <v>14418453.5</v>
+        <v>2688211.3</v>
       </c>
       <c r="N23" t="n">
-        <v>15172146.925</v>
+        <v>1792966.675</v>
       </c>
       <c r="O23" t="n">
-        <v>1.497516387593163</v>
+        <v>0.8195304439052095</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.372661754096583</v>
+        <v>0.4796668846000181</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.05517236074451376</v>
+        <v>0.57480065939164</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.317489393352069</v>
+        <v>-0.09513377479162199</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.322068438919912</v>
+        <v>0.0017609374454155</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.120971282913056</v>
+        <v>0.08131621380420762</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3785,48 +3785,48 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>9723.733</v>
+        <v>406.644</v>
       </c>
       <c r="AC23" t="n">
-        <v>559.758</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>299.131</v>
+        <v>31</v>
       </c>
       <c r="AE23" t="n">
-        <v>10582.622</v>
+        <v>437.644</v>
       </c>
       <c r="AF23" t="n">
-        <v>14833.221</v>
+        <v>1256.458</v>
       </c>
       <c r="AG23" t="n">
-        <v>10554.223</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>-1494.05</v>
+        <v>42</v>
       </c>
       <c r="AI23" t="n">
-        <v>23893.394</v>
+        <v>1298.458</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-15346.904</v>
+        <v>1814.151</v>
       </c>
       <c r="AK23" t="n">
-        <v>39133.79300000001</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>-505.3599999999998</v>
+        <v>41.99999999999999</v>
       </c>
       <c r="AM23" t="n">
-        <v>23281.529</v>
+        <v>1856.151</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3837,16 +3837,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>隴華</t>
+          <t>統領</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3855,49 +3855,49 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9.609999656677246</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="G24" t="n">
-        <v>10.32749996185303</v>
+        <v>22.75250015258789</v>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.52938126786281</v>
+        <v>52.31833414671451</v>
       </c>
       <c r="J24" t="n">
-        <v>37.23372410947275</v>
+        <v>34.879266309904</v>
       </c>
       <c r="K24" t="n">
-        <v>35.31840433949638</v>
+        <v>71.12345025059163</v>
       </c>
       <c r="L24" t="n">
-        <v>167122.6</v>
+        <v>121156.8</v>
       </c>
       <c r="M24" t="n">
-        <v>122409.2</v>
+        <v>49302.8</v>
       </c>
       <c r="N24" t="n">
-        <v>147914.75</v>
+        <v>30357.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.365278100012091</v>
+        <v>2.457402013678736</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.037048455627199</v>
+        <v>0.2091113421501518</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.288918057853476</v>
+        <v>0.1354173747552232</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2518696022262776</v>
+        <v>0.07369396739492864</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2866204166512802</v>
+        <v>-0.07548873045352085</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2878646776892462</v>
+        <v>-0.08489118665591353</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3906,17 +3906,17 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3935,44 +3935,44 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>-2.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>9</v>
+        <v>53.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2</v>
+        <v>-1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>113</v>
+        <v>57.8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>118</v>
+        <v>113.224</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>113.024</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3983,67 +3983,67 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>30.60000038146973</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>32.19000015258789</v>
+        <v>77.74499969482422</v>
       </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>37.89033463956294</v>
+        <v>77.98973441328917</v>
       </c>
       <c r="J25" t="n">
-        <v>41.32712311606021</v>
+        <v>74.41591713693958</v>
       </c>
       <c r="K25" t="n">
-        <v>34.37324282893074</v>
+        <v>53.5720281146323</v>
       </c>
       <c r="L25" t="n">
-        <v>2905.4</v>
+        <v>128986.2</v>
       </c>
       <c r="M25" t="n">
-        <v>2186.1</v>
+        <v>57339.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1910.3</v>
+        <v>62888.85</v>
       </c>
       <c r="O25" t="n">
-        <v>1.329033438543525</v>
+        <v>2.249507540580487</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.492400284986612</v>
+        <v>0.03387606041756897</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.560927498500285</v>
+        <v>0.01189584493200951</v>
       </c>
       <c r="R25" t="n">
-        <v>0.06852721351367252</v>
+        <v>0.02198021548555946</v>
       </c>
       <c r="S25" t="n">
-        <v>0.07231612396605369</v>
+        <v>0.005357696724183507</v>
       </c>
       <c r="T25" t="n">
-        <v>0.09526649057433634</v>
+        <v>-0.02170397707746514</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4052,17 +4052,17 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4081,44 +4081,44 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>105.105</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>106.105</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>129.21</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>135.21</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -4129,16 +4129,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>寶齡富錦</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4147,49 +4147,49 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>60.90000152587891</v>
+        <v>23.79999923706055</v>
       </c>
       <c r="G26" t="n">
-        <v>61.44500064849854</v>
+        <v>23.31750001907348</v>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>32.78091078638468</v>
+        <v>53.6015573620247</v>
       </c>
       <c r="J26" t="n">
-        <v>48.54242812348657</v>
+        <v>46.47206631474066</v>
       </c>
       <c r="K26" t="n">
-        <v>45.49865503393516</v>
+        <v>53.22009348054807</v>
       </c>
       <c r="L26" t="n">
-        <v>264461.6</v>
+        <v>297668.2</v>
       </c>
       <c r="M26" t="n">
-        <v>244802.65</v>
+        <v>163674.95</v>
       </c>
       <c r="N26" t="n">
-        <v>226040.8</v>
+        <v>176643.425</v>
       </c>
       <c r="O26" t="n">
-        <v>1.08030529898267</v>
+        <v>1.818654595587168</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3741915727702718</v>
+        <v>-0.102562553206841</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2890807651284776</v>
+        <v>-0.2270152242848617</v>
       </c>
       <c r="R26" t="n">
-        <v>0.08511080764179418</v>
+        <v>0.1244526710780207</v>
       </c>
       <c r="S26" t="n">
-        <v>0.267580613325183</v>
+        <v>0.1055602776801123</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4000645487671448</v>
+        <v>-0.03656496764793371</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -4198,17 +4198,17 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4227,44 +4227,44 @@
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>-46</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>-45</v>
+        <v>80</v>
       </c>
       <c r="AF26" t="n">
-        <v>130.195</v>
+        <v>78.69</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1</v>
+        <v>4.297000000000001</v>
       </c>
       <c r="AI26" t="n">
-        <v>129.195</v>
+        <v>82.98699999999999</v>
       </c>
       <c r="AJ26" t="n">
-        <v>611.888</v>
+        <v>-184.77</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>5.79</v>
+        <v>16.297</v>
       </c>
       <c r="AM26" t="n">
-        <v>617.678</v>
+        <v>-168.473</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -4279,63 +4279,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>統領</t>
+          <t>友鋮</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>22.35000038146973</v>
+        <v>47.5</v>
       </c>
       <c r="G27" t="n">
-        <v>22.63750019073486</v>
+        <v>47.08500022888184</v>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>28.47750121955022</v>
+        <v>45.78816273250214</v>
       </c>
       <c r="J27" t="n">
-        <v>26.15973238176345</v>
+        <v>36.14440392322234</v>
       </c>
       <c r="K27" t="n">
-        <v>51.15065580889376</v>
+        <v>53.54420837196371</v>
       </c>
       <c r="L27" t="n">
-        <v>84800.2</v>
+        <v>38610</v>
       </c>
       <c r="M27" t="n">
-        <v>39463.65</v>
+        <v>22113.1</v>
       </c>
       <c r="N27" t="n">
-        <v>25237.575</v>
+        <v>30754.775</v>
       </c>
       <c r="O27" t="n">
-        <v>2.148817962859492</v>
+        <v>1.746023850115995</v>
       </c>
       <c r="P27" t="n">
-        <v>0.04658353382096081</v>
+        <v>-0.3072768842329978</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1244248516868559</v>
+        <v>-0.3706699505160868</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.07784131786589504</v>
+        <v>0.06339306628308894</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.08742742888139421</v>
+        <v>0.006157129989027177</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.09750239640281574</v>
+        <v>-0.01387110799574609</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4373,40 +4373,40 @@
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>65.224</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>67.224</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4425,63 +4425,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>友鋮</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>47.5</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>47.08500022888184</v>
+        <v>12.35999999046326</v>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>45.788162730293</v>
+        <v>27.85058193837805</v>
       </c>
       <c r="J28" t="n">
-        <v>36.14440388198501</v>
+        <v>35.57944019519256</v>
       </c>
       <c r="K28" t="n">
-        <v>50.9526826830939</v>
+        <v>23.85582022864324</v>
       </c>
       <c r="L28" t="n">
-        <v>38614.4</v>
+        <v>1118125.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22114.2</v>
+        <v>652955.1</v>
       </c>
       <c r="N28" t="n">
-        <v>30755.325</v>
+        <v>586396.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.746135966935272</v>
+        <v>1.712407790367209</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.3111833337317478</v>
+        <v>-0.1881154541173888</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.3763860837018073</v>
+        <v>-0.1469790489922898</v>
       </c>
       <c r="R28" t="n">
-        <v>0.06520274997005948</v>
+        <v>-0.04113640512509903</v>
       </c>
       <c r="S28" t="n">
-        <v>0.008108086692063421</v>
+        <v>-0.02583218333351384</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.01176820311795035</v>
+        <v>-0.00744795300514503</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4519,44 +4519,44 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>48.41</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>70.41</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>30.849</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>45.849</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000.841</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1023.841</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>連宇</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4585,49 +4585,49 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>18.20000076293945</v>
+        <v>20.54999923706055</v>
       </c>
       <c r="G29" t="n">
-        <v>17.21999998092651</v>
+        <v>21.02749977111817</v>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>54.94095041662696</v>
+        <v>35.50275097973773</v>
       </c>
       <c r="J29" t="n">
-        <v>46.44271693108152</v>
+        <v>44.27420908322494</v>
       </c>
       <c r="K29" t="n">
-        <v>66.19459910240832</v>
+        <v>39.48459134939345</v>
       </c>
       <c r="L29" t="n">
-        <v>638598.4</v>
+        <v>256059.6</v>
       </c>
       <c r="M29" t="n">
-        <v>382654.45</v>
+        <v>187166.65</v>
       </c>
       <c r="N29" t="n">
-        <v>292185.2</v>
+        <v>203448.175</v>
       </c>
       <c r="O29" t="n">
-        <v>1.668864428468034</v>
+        <v>1.368083469998528</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2330921958405696</v>
+        <v>-0.07867396908310553</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1272544961343215</v>
+        <v>0.009820819643671187</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1058376997062481</v>
+        <v>-0.08849478872677671</v>
       </c>
       <c r="S29" t="n">
-        <v>0.07140988742694174</v>
+        <v>-0.08625040128160988</v>
       </c>
       <c r="T29" t="n">
-        <v>0.06504342091879509</v>
+        <v>-0.08610241774491934</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4636,17 +4636,17 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4665,44 +4665,44 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>219.034</v>
+        <v>70</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.026</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>220.06</v>
+        <v>77</v>
       </c>
       <c r="AF29" t="n">
-        <v>229.034</v>
+        <v>-46.651</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>-8.359</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
-        <v>220.675</v>
+        <v>-34.651</v>
       </c>
       <c r="AJ29" t="n">
-        <v>435.0600000000001</v>
+        <v>399.974</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.472</v>
+        <v>12</v>
       </c>
       <c r="AM29" t="n">
-        <v>435.5319999999999</v>
+        <v>411.974</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -4717,63 +4717,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>大東電</t>
+          <t>集雅社</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>231.5</v>
+        <v>47.5</v>
       </c>
       <c r="G30" t="n">
-        <v>219.425</v>
+        <v>48.44249992370605</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>54.0811436065183</v>
+        <v>46.27930819189135</v>
       </c>
       <c r="J30" t="n">
-        <v>50.46935050461531</v>
+        <v>45.93871171290229</v>
       </c>
       <c r="K30" t="n">
-        <v>57.58347915102494</v>
+        <v>45.00479107739616</v>
       </c>
       <c r="L30" t="n">
-        <v>593091.6</v>
+        <v>8408</v>
       </c>
       <c r="M30" t="n">
-        <v>371831.8</v>
+        <v>6412.5</v>
       </c>
       <c r="N30" t="n">
-        <v>339040.65</v>
+        <v>7578.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.595053462345071</v>
+        <v>1.311189083820663</v>
       </c>
       <c r="P30" t="n">
-        <v>1.704196066142373</v>
+        <v>-0.05407916947116576</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.2873239161383161</v>
+        <v>0.1147914030646107</v>
       </c>
       <c r="R30" t="n">
-        <v>1.991519982280689</v>
+        <v>-0.1688705725357765</v>
       </c>
       <c r="S30" t="n">
-        <v>1.903840219340817</v>
+        <v>-0.1718931646304488</v>
       </c>
       <c r="T30" t="n">
-        <v>2.125232927021317</v>
+        <v>-0.1748044844676204</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4782,17 +4782,17 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4811,44 +4811,44 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>23.995</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>35.073</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>59.068</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1086.233</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>-283.794</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>802.4390000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1430.484</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>-992.105</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>438.379</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>台驊控股</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4877,49 +4877,49 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>82.5</v>
+        <v>68.59999847412109</v>
       </c>
       <c r="G31" t="n">
-        <v>91.55000038146973</v>
+        <v>70.11499938964843</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>15.65555922580914</v>
+        <v>32.65212882343811</v>
       </c>
       <c r="J31" t="n">
-        <v>23.81892275355593</v>
+        <v>47.77370018838155</v>
       </c>
       <c r="K31" t="n">
-        <v>34.04388206093381</v>
+        <v>42.12656051296092</v>
       </c>
       <c r="L31" t="n">
-        <v>12453348.8</v>
+        <v>501949</v>
       </c>
       <c r="M31" t="n">
-        <v>8701913.449999999</v>
+        <v>399457.85</v>
       </c>
       <c r="N31" t="n">
-        <v>9076091.15</v>
+        <v>447426.05</v>
       </c>
       <c r="O31" t="n">
-        <v>1.431104649748039</v>
+        <v>1.256575631196132</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.2682573810885458</v>
+        <v>0.1920271019665734</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9355652307628128</v>
+        <v>0.3997653089392494</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.203822611851359</v>
+        <v>-0.2077382069726761</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.7931532212438761</v>
+        <v>-0.09544905314606311</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.7005072733066493</v>
+        <v>-0.02688382498001063</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4953,48 +4953,48 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB31" t="n">
-        <v>11472.068</v>
+        <v>-391.803</v>
       </c>
       <c r="AC31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>-3648.654</v>
+        <v>31.545</v>
       </c>
       <c r="AE31" t="n">
-        <v>7829.413999999999</v>
+        <v>-360.258</v>
       </c>
       <c r="AF31" t="n">
-        <v>-13651.406</v>
+        <v>-699.205</v>
       </c>
       <c r="AG31" t="n">
-        <v>8769.905999999999</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>-6207.718000000001</v>
+        <v>17.54</v>
       </c>
       <c r="AI31" t="n">
-        <v>-11089.218</v>
+        <v>-681.6650000000001</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-24571.168</v>
+        <v>-542.888</v>
       </c>
       <c r="AK31" t="n">
-        <v>12499.666</v>
+        <v>2</v>
       </c>
       <c r="AL31" t="n">
-        <v>-4820.553</v>
+        <v>227.971</v>
       </c>
       <c r="AM31" t="n">
-        <v>-16892.055</v>
+        <v>-312.9169999999999</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -5009,72 +5009,72 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>集雅社</t>
+          <t>黑松</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>47.59999847412109</v>
+        <v>33.45000076293945</v>
       </c>
       <c r="G32" t="n">
-        <v>48.48499984741211</v>
+        <v>33.96000022888184</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>48.68728447055811</v>
+        <v>53.96026134500078</v>
       </c>
       <c r="J32" t="n">
-        <v>45.76841345199004</v>
+        <v>34.01076517558803</v>
       </c>
       <c r="K32" t="n">
-        <v>46.19965881036515</v>
+        <v>40.35990083763099</v>
       </c>
       <c r="L32" t="n">
-        <v>9207.4</v>
+        <v>136548.4</v>
       </c>
       <c r="M32" t="n">
-        <v>7012.35</v>
+        <v>173892.25</v>
       </c>
       <c r="N32" t="n">
-        <v>7628.575</v>
+        <v>164706.275</v>
       </c>
       <c r="O32" t="n">
-        <v>1.313026303592947</v>
+        <v>0.7852471861166901</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.01332153267161829</v>
+        <v>-0.4089827947953495</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1592955081949741</v>
+        <v>-0.3722496847097924</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.1726170408665924</v>
+        <v>-0.03673311008555713</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.1755848701257571</v>
+        <v>-0.07329473773370659</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.2042159473443973</v>
+        <v>-0.1049431988587589</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5103,44 +5103,44 @@
         </is>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>103.35</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>117.35</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>230.972</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>-2.388</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>228.584</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>550.992</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>3.575000000000002</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>554.5669999999999</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>潤隆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5169,53 +5169,53 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>20.64999961853027</v>
+        <v>30.70000076293945</v>
       </c>
       <c r="G33" t="n">
-        <v>21.04749984741211</v>
+        <v>30.67250003814697</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>37.18273438738547</v>
+        <v>42.50343264356408</v>
       </c>
       <c r="J33" t="n">
-        <v>48.65993807071511</v>
+        <v>37.17541551991434</v>
       </c>
       <c r="K33" t="n">
-        <v>42.12436052875002</v>
+        <v>51.79055752878181</v>
       </c>
       <c r="L33" t="n">
-        <v>232017.8</v>
+        <v>533680.2</v>
       </c>
       <c r="M33" t="n">
-        <v>182406.45</v>
+        <v>1231814.85</v>
       </c>
       <c r="N33" t="n">
-        <v>197980.45</v>
+        <v>1647775.675</v>
       </c>
       <c r="O33" t="n">
-        <v>1.271982432638758</v>
+        <v>0.43324709066464</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.05352459157609957</v>
+        <v>0.001413675603004094</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.03308774782357957</v>
+        <v>0.03556898882842529</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.08661233939967913</v>
+        <v>-0.0341553132254212</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.08649261057398457</v>
+        <v>-0.06490108025545367</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.04422748906149529</v>
+        <v>-0.1193496947372072</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5249,44 +5249,44 @@
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>-17</v>
+        <v>370.419</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AE33" t="n">
-        <v>-12</v>
+        <v>399.419</v>
       </c>
       <c r="AF33" t="n">
-        <v>-63.65100000000001</v>
+        <v>501.5369999999999</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI33" t="n">
-        <v>-59.65100000000001</v>
+        <v>511.5369999999999</v>
       </c>
       <c r="AJ33" t="n">
-        <v>354.974</v>
+        <v>-1319.16</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AM33" t="n">
-        <v>359.974</v>
+        <v>-1283.16</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -5297,16 +5297,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>訊聯</t>
+          <t>鐿鈦</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5315,49 +5315,49 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>66.5</v>
+        <v>127</v>
       </c>
       <c r="G34" t="n">
-        <v>68.03499984741211</v>
+        <v>125.1</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>31.9760589792391</v>
+        <v>27.05385043587792</v>
       </c>
       <c r="J34" t="n">
-        <v>44.47198285478845</v>
+        <v>38.7579810159428</v>
       </c>
       <c r="K34" t="n">
-        <v>45.21656718995503</v>
+        <v>53.61488562249074</v>
       </c>
       <c r="L34" t="n">
-        <v>305449.2</v>
+        <v>441103</v>
       </c>
       <c r="M34" t="n">
-        <v>247948.1</v>
+        <v>238821.9</v>
       </c>
       <c r="N34" t="n">
-        <v>252334.3</v>
+        <v>261280.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.231907806512734</v>
+        <v>1.846995606349334</v>
       </c>
       <c r="P34" t="n">
-        <v>0.03242427295108996</v>
+        <v>3.22970732589684</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.115784416649745</v>
+        <v>3.580951940150844</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1482086896008349</v>
+        <v>-0.3512446142540044</v>
       </c>
       <c r="S34" t="n">
-        <v>0.3999016110708021</v>
+        <v>-0.1723710359814543</v>
       </c>
       <c r="T34" t="n">
-        <v>0.5055158704203563</v>
+        <v>0.1758844691814501</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5366,17 +5366,17 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -5443,16 +5443,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>向榮生技</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5461,49 +5461,49 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>79.80000305175781</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>80.10000038146973</v>
+        <v>11.09499998092651</v>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>57.00392878741368</v>
+        <v>48.47488478563373</v>
       </c>
       <c r="J35" t="n">
-        <v>60.00490051030581</v>
+        <v>54.06068394355765</v>
       </c>
       <c r="K35" t="n">
-        <v>47.16558810788344</v>
+        <v>50.73285671752497</v>
       </c>
       <c r="L35" t="n">
-        <v>70719</v>
+        <v>7585125.2</v>
       </c>
       <c r="M35" t="n">
-        <v>57629.9</v>
+        <v>4326823.6</v>
       </c>
       <c r="N35" t="n">
-        <v>51416.475</v>
+        <v>3770678.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.227123420307861</v>
+        <v>1.753047015829349</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3622027959684573</v>
+        <v>0.06540677782030713</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1168789769604429</v>
+        <v>0.01780102562856227</v>
       </c>
       <c r="R35" t="n">
-        <v>0.2453238190080143</v>
+        <v>0.04760575219174486</v>
       </c>
       <c r="S35" t="n">
-        <v>0.4677474556733064</v>
+        <v>0.06747330008342553</v>
       </c>
       <c r="T35" t="n">
-        <v>0.5179584729176151</v>
+        <v>0.09344203602972857</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5541,44 +5541,44 @@
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>-13</v>
+        <v>-1156</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AE35" t="n">
-        <v>-13</v>
+        <v>-1053</v>
       </c>
       <c r="AF35" t="n">
-        <v>39</v>
+        <v>-8088.9</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>195.114</v>
       </c>
       <c r="AI35" t="n">
-        <v>39</v>
+        <v>-7893.786</v>
       </c>
       <c r="AJ35" t="n">
-        <v>38.15</v>
+        <v>-2734.206</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2</v>
+        <v>156.787</v>
       </c>
       <c r="AM35" t="n">
-        <v>40.15</v>
+        <v>-2577.418999999999</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -5589,67 +5589,67 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>佳世達</t>
+          <t>德麥</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>31</v>
+        <v>271.5</v>
       </c>
       <c r="G36" t="n">
-        <v>31.94500007629394</v>
+        <v>270.2</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>36.80853204004609</v>
+        <v>50.35783090039538</v>
       </c>
       <c r="J36" t="n">
-        <v>53.85130012397743</v>
+        <v>53.27998098897451</v>
       </c>
       <c r="K36" t="n">
-        <v>48.00502162317317</v>
+        <v>53.66126194506403</v>
       </c>
       <c r="L36" t="n">
-        <v>26557372.2</v>
+        <v>46768</v>
       </c>
       <c r="M36" t="n">
-        <v>21830605.55</v>
+        <v>30761.6</v>
       </c>
       <c r="N36" t="n">
-        <v>18929723.2</v>
+        <v>33015.45</v>
       </c>
       <c r="O36" t="n">
-        <v>1.216520180311718</v>
+        <v>1.52033704358681</v>
       </c>
       <c r="P36" t="n">
-        <v>0.931327482038899</v>
+        <v>0.07676685366686797</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.090045596420651</v>
+        <v>-0.0932104941644277</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.1587181143817524</v>
+        <v>0.1699773478312957</v>
       </c>
       <c r="S36" t="n">
-        <v>0.03414756054748924</v>
+        <v>0.1116763107247439</v>
       </c>
       <c r="T36" t="n">
-        <v>0.118931271393119</v>
+        <v>0.2149297076240732</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5663,12 +5663,12 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5683,48 +5683,48 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>-4166.301</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>-324.722</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>-4491.023</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>-25899.508</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>10911</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>-534.6879999999999</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>-15523.196</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>-42793.031</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>44382</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>-383.7939999999999</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1205.174999999997</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -5735,67 +5735,67 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>智伸科</t>
+          <t>海灣</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>214</v>
+        <v>17.39999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>230.375</v>
+        <v>17.64750022888184</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>27.91626446481996</v>
+        <v>26.43640383200383</v>
       </c>
       <c r="J37" t="n">
-        <v>45.8161269419944</v>
+        <v>25.90441749903176</v>
       </c>
       <c r="K37" t="n">
-        <v>49.75548679773379</v>
+        <v>39.7811657568821</v>
       </c>
       <c r="L37" t="n">
-        <v>2160009.8</v>
+        <v>36000.2</v>
       </c>
       <c r="M37" t="n">
-        <v>1946993.15</v>
+        <v>25639.75</v>
       </c>
       <c r="N37" t="n">
-        <v>1569122.125</v>
+        <v>26305</v>
       </c>
       <c r="O37" t="n">
-        <v>1.109408012041542</v>
+        <v>1.40407765286323</v>
       </c>
       <c r="P37" t="n">
-        <v>17.27787046607099</v>
+        <v>-0.1235000649601474</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.98147253421886</v>
+        <v>-0.130992488235538</v>
       </c>
       <c r="R37" t="n">
-        <v>-4.703602068147866</v>
+        <v>0.00749242327539057</v>
       </c>
       <c r="S37" t="n">
-        <v>-2.539941909329109</v>
+        <v>0.02332989785977685</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.7905053042698924</v>
+        <v>0.03839737428956033</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5833,44 +5833,44 @@
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>710.241</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>-11.055</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>654.186</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1378.343</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>-717</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>-47.696</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>613.6469999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>4927.800999999999</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>-1487</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>167.829</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>3608.63</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -5885,63 +5885,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>西勝</t>
+          <t>州巧</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>16.85000038146973</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>16.53499989509583</v>
+        <v>30.47000017166138</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>45.27808192613711</v>
+        <v>54.55817359252779</v>
       </c>
       <c r="J38" t="n">
-        <v>51.98033757003852</v>
+        <v>53.53444536154821</v>
       </c>
       <c r="K38" t="n">
-        <v>53.71508065040771</v>
+        <v>46.52333422706964</v>
       </c>
       <c r="L38" t="n">
-        <v>1362363.8</v>
+        <v>1326289.8</v>
       </c>
       <c r="M38" t="n">
-        <v>803332.95</v>
+        <v>1015242.45</v>
       </c>
       <c r="N38" t="n">
-        <v>665106.75</v>
+        <v>960306.55</v>
       </c>
       <c r="O38" t="n">
-        <v>1.695889356959652</v>
+        <v>1.306377407682273</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4864680436923763</v>
+        <v>-0.6050010405152406</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4338124496725494</v>
+        <v>-1.112159486411015</v>
       </c>
       <c r="R38" t="n">
-        <v>0.05265559401982689</v>
+        <v>0.5071584458957745</v>
       </c>
       <c r="S38" t="n">
-        <v>0.116726492823395</v>
+        <v>0.5833888067955721</v>
       </c>
       <c r="T38" t="n">
-        <v>0.17252221890616</v>
+        <v>0.7149666758823952</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5955,12 +5955,12 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>-60.8</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5988,35 +5988,35 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>-60.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>-2801.258</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>-0.7470000000000006</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>-2802.005</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>-1944.718</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>-1945.718</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -6031,12 +6031,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>大亞</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -6045,49 +6045,49 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>40.09999847412109</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="G39" t="n">
-        <v>38.625</v>
+        <v>91.17000045776368</v>
       </c>
       <c r="H39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>42.53062078957601</v>
+        <v>15.6222161923942</v>
       </c>
       <c r="J39" t="n">
-        <v>52.83548822129333</v>
+        <v>21.08668724140624</v>
       </c>
       <c r="K39" t="n">
-        <v>55.40350255713273</v>
+        <v>35.63669587589783</v>
       </c>
       <c r="L39" t="n">
-        <v>16138534.8</v>
+        <v>11890314.2</v>
       </c>
       <c r="M39" t="n">
-        <v>10612065.55</v>
+        <v>9102884.25</v>
       </c>
       <c r="N39" t="n">
-        <v>12511609.625</v>
+        <v>9284041.775</v>
       </c>
       <c r="O39" t="n">
-        <v>1.520772249658786</v>
+        <v>1.306213928843487</v>
       </c>
       <c r="P39" t="n">
-        <v>0.8346658951188175</v>
+        <v>-0.7763254191273177</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.7736557365138489</v>
+        <v>0.5913579660761629</v>
       </c>
       <c r="R39" t="n">
-        <v>0.06101015860496861</v>
+        <v>-1.367683385203481</v>
       </c>
       <c r="S39" t="n">
-        <v>0.07250019447665579</v>
+        <v>-1.203098749422033</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1755552343977038</v>
+        <v>-0.792372850470388</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -6116,53 +6116,53 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>668.117</v>
+        <v>2138.149</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="AD39" t="n">
-        <v>63.763</v>
+        <v>1418.069</v>
       </c>
       <c r="AE39" t="n">
-        <v>731.88</v>
+        <v>4182.218</v>
       </c>
       <c r="AF39" t="n">
-        <v>7634.181</v>
+        <v>-4225.085000000002</v>
       </c>
       <c r="AG39" t="n">
-        <v>-3</v>
+        <v>5168.801</v>
       </c>
       <c r="AH39" t="n">
-        <v>-68.95799999999997</v>
+        <v>-4892.943000000001</v>
       </c>
       <c r="AI39" t="n">
-        <v>7562.223000000001</v>
+        <v>-3949.227000000002</v>
       </c>
       <c r="AJ39" t="n">
-        <v>10213.23</v>
+        <v>-21457.899</v>
       </c>
       <c r="AK39" t="n">
-        <v>-4</v>
+        <v>14331.86400000001</v>
       </c>
       <c r="AL39" t="n">
-        <v>479.6569999999999</v>
+        <v>-3572.087</v>
       </c>
       <c r="AM39" t="n">
-        <v>10688.887</v>
+        <v>-10698.122</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -6177,63 +6177,63 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>17.25</v>
+        <v>69.09999847412109</v>
       </c>
       <c r="G40" t="n">
-        <v>17.41749982833862</v>
+        <v>68.51500015258789</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>52.05890769321407</v>
+        <v>41.17795565388872</v>
       </c>
       <c r="J40" t="n">
-        <v>63.25449274361483</v>
+        <v>49.22041637763359</v>
       </c>
       <c r="K40" t="n">
-        <v>43.58437628489185</v>
+        <v>50.03715793076051</v>
       </c>
       <c r="L40" t="n">
-        <v>109519</v>
+        <v>2192091</v>
       </c>
       <c r="M40" t="n">
-        <v>77085.64999999999</v>
+        <v>1726374.3</v>
       </c>
       <c r="N40" t="n">
-        <v>88917.77499999999</v>
+        <v>1482120.85</v>
       </c>
       <c r="O40" t="n">
-        <v>1.420744327900199</v>
+        <v>1.269765774432578</v>
       </c>
       <c r="P40" t="n">
-        <v>0.05390603344579858</v>
+        <v>0.9050747674920245</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.01373096725012691</v>
+        <v>0.7468941150270112</v>
       </c>
       <c r="R40" t="n">
-        <v>0.06763700069592549</v>
+        <v>0.1581806524650133</v>
       </c>
       <c r="S40" t="n">
-        <v>0.1292387468271141</v>
+        <v>0.358570112539299</v>
       </c>
       <c r="T40" t="n">
-        <v>0.1357036819908806</v>
+        <v>0.4343678114903847</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6242,12 +6242,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6271,44 +6271,44 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>141.051</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>135.051</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6337,49 +6337,49 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>64.69999694824219</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="G41" t="n">
-        <v>66.74499950408935</v>
+        <v>8.597499895095826</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>43.82034743874213</v>
+        <v>33.04604739752948</v>
       </c>
       <c r="J41" t="n">
-        <v>50.25651228095195</v>
+        <v>48.71029772907877</v>
       </c>
       <c r="K41" t="n">
-        <v>46.81457711924104</v>
+        <v>53.11753170424657</v>
       </c>
       <c r="L41" t="n">
-        <v>50995988.6</v>
+        <v>122246655.8</v>
       </c>
       <c r="M41" t="n">
-        <v>36105813.95</v>
+        <v>96918746.5</v>
       </c>
       <c r="N41" t="n">
-        <v>74721651.8</v>
+        <v>67458918.95</v>
       </c>
       <c r="O41" t="n">
-        <v>1.412403793766295</v>
+        <v>1.261331375143198</v>
       </c>
       <c r="P41" t="n">
-        <v>0.7703373971385901</v>
+        <v>0.3816544280014007</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.07300913593986</v>
+        <v>0.418195146914436</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.3026717388012701</v>
+        <v>-0.03654071891303534</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.07843859797212538</v>
+        <v>0.004433015365362669</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.2501058739315865</v>
+        <v>0.0520182086920144</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6388,12 +6388,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -6413,48 +6413,48 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>-26602.157</v>
+        <v>-6527.216</v>
       </c>
       <c r="AC41" t="n">
-        <v>2902.299</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>-762.23</v>
+        <v>-139.136</v>
       </c>
       <c r="AE41" t="n">
-        <v>-24462.088</v>
+        <v>-6666.352000000001</v>
       </c>
       <c r="AF41" t="n">
-        <v>-42758.35799999999</v>
+        <v>-97891.709</v>
       </c>
       <c r="AG41" t="n">
-        <v>20342.573</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>111.134</v>
+        <v>-2886.069</v>
       </c>
       <c r="AI41" t="n">
-        <v>-22304.651</v>
+        <v>-100777.778</v>
       </c>
       <c r="AJ41" t="n">
-        <v>-77879.25399999999</v>
+        <v>61443.677</v>
       </c>
       <c r="AK41" t="n">
-        <v>43231.304</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>3379.161</v>
+        <v>-989.0429999999999</v>
       </c>
       <c r="AM41" t="n">
-        <v>-31268.789</v>
+        <v>60454.63400000001</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6483,49 +6483,49 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>59.70000076293945</v>
+        <v>40.79999923706055</v>
       </c>
       <c r="G42" t="n">
-        <v>61.60179634094239</v>
+        <v>42.4375</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>29.7543885647677</v>
+        <v>28.84968609100698</v>
       </c>
       <c r="J42" t="n">
-        <v>32.31325315015918</v>
+        <v>30.44483783417952</v>
       </c>
       <c r="K42" t="n">
-        <v>43.3034493503291</v>
+        <v>49.49495224610204</v>
       </c>
       <c r="L42" t="n">
-        <v>1384957</v>
+        <v>71185871.2</v>
       </c>
       <c r="M42" t="n">
-        <v>984816.45</v>
+        <v>67127118.15000001</v>
       </c>
       <c r="N42" t="n">
-        <v>916999</v>
+        <v>64058538.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.406309774780874</v>
+        <v>1.060463686835631</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.5119597067640669</v>
+        <v>0.5200253654995137</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.1934071671346386</v>
+        <v>1.151676700608282</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.3185525396294283</v>
+        <v>-0.6316513351087678</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.3520263124132443</v>
+        <v>-0.6841050237534532</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.3437897955288566</v>
+        <v>-0.7245341868311621</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6563,44 +6563,44 @@
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>150.75</v>
+        <v>45290.931</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>-2289.819</v>
       </c>
       <c r="AD42" t="n">
-        <v>8.627000000000001</v>
+        <v>1288.439</v>
       </c>
       <c r="AE42" t="n">
-        <v>159.377</v>
+        <v>44289.55099999999</v>
       </c>
       <c r="AF42" t="n">
-        <v>-471.001</v>
+        <v>213984.721</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>-12935.761</v>
       </c>
       <c r="AH42" t="n">
-        <v>11.284</v>
+        <v>-6568.509000000001</v>
       </c>
       <c r="AI42" t="n">
-        <v>-459.717</v>
+        <v>194480.451</v>
       </c>
       <c r="AJ42" t="n">
-        <v>-1873.391</v>
+        <v>357668.762</v>
       </c>
       <c r="AK42" t="n">
-        <v>-331</v>
+        <v>22280.023</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.7339999999999947</v>
+        <v>1464.943999999999</v>
       </c>
       <c r="AM42" t="n">
-        <v>-2205.125</v>
+        <v>381413.7290000001</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -6615,67 +6615,67 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>16.35000038146973</v>
+        <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>16.54249982833862</v>
+        <v>46.09499988555908</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>28.36937164293926</v>
+        <v>52.00739241558795</v>
       </c>
       <c r="J43" t="n">
-        <v>41.95213453044207</v>
+        <v>42.31447174413942</v>
       </c>
       <c r="K43" t="n">
-        <v>49.45949785474885</v>
+        <v>52.32075166509529</v>
       </c>
       <c r="L43" t="n">
-        <v>922866.8</v>
+        <v>845714.8</v>
       </c>
       <c r="M43" t="n">
-        <v>658982.1</v>
+        <v>1823142.05</v>
       </c>
       <c r="N43" t="n">
-        <v>362242.575</v>
+        <v>1993209.75</v>
       </c>
       <c r="O43" t="n">
-        <v>1.400442895186379</v>
+        <v>0.4638776227008751</v>
       </c>
       <c r="P43" t="n">
-        <v>0.5204734041225265</v>
+        <v>0.01446696004240522</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5825698517829854</v>
+        <v>0.0579636184341439</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.06209644766045885</v>
+        <v>-0.04349665839173868</v>
       </c>
       <c r="S43" t="n">
-        <v>0.02624725158930497</v>
+        <v>-0.08089901272128765</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1104827695818249</v>
+        <v>-0.1449896093649889</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -6695,58 +6695,58 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>332.691</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>566.691</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1132.903</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>172.81</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>24.706</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1330.419</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>-3471.591</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2078.114</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>896.9369999999999</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>-496.5399999999997</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -6757,16 +6757,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>怡利電</t>
+          <t>威強電</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6775,49 +6775,49 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>61.59999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="G44" t="n">
-        <v>60.06000022888183</v>
+        <v>85.35000076293946</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>43.5977450935901</v>
+        <v>44.46717006477275</v>
       </c>
       <c r="J44" t="n">
-        <v>48.1085326991301</v>
+        <v>54.74030692594214</v>
       </c>
       <c r="K44" t="n">
-        <v>54.03553637187837</v>
+        <v>54.39504682840241</v>
       </c>
       <c r="L44" t="n">
-        <v>1210543.4</v>
+        <v>3300048.4</v>
       </c>
       <c r="M44" t="n">
-        <v>891877.1</v>
+        <v>2344915.9</v>
       </c>
       <c r="N44" t="n">
-        <v>1096790.95</v>
+        <v>2331177.275</v>
       </c>
       <c r="O44" t="n">
-        <v>1.357298443922375</v>
+        <v>1.407320578106874</v>
       </c>
       <c r="P44" t="n">
-        <v>0.5989999887149153</v>
+        <v>2.648003156277042</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.3486443100232657</v>
+        <v>2.796269767284429</v>
       </c>
       <c r="R44" t="n">
-        <v>0.2503556786916497</v>
+        <v>-0.1482666110073865</v>
       </c>
       <c r="S44" t="n">
-        <v>0.3053388019944617</v>
+        <v>0.1074890747564727</v>
       </c>
       <c r="T44" t="n">
-        <v>0.4448181110109224</v>
+        <v>0.2616971210450321</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6855,44 +6855,44 @@
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>16.346</v>
+        <v>275.871</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.722</v>
+        <v>-6.825</v>
       </c>
       <c r="AE44" t="n">
-        <v>15.624</v>
+        <v>269.046</v>
       </c>
       <c r="AF44" t="n">
-        <v>1504.308</v>
+        <v>1997.672</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>5.677</v>
+        <v>-14.86</v>
       </c>
       <c r="AI44" t="n">
-        <v>1509.985</v>
+        <v>1982.812</v>
       </c>
       <c r="AJ44" t="n">
-        <v>730.0110000000001</v>
+        <v>190.6989999999999</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>38.659</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.5280000000000005</v>
+        <v>31.31699999999999</v>
       </c>
       <c r="AM44" t="n">
-        <v>730.5390000000001</v>
+        <v>260.6749999999999</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -6903,67 +6903,67 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>皇鼎</t>
+          <t>耕興</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>13.55000019073486</v>
+        <v>190.5</v>
       </c>
       <c r="G45" t="n">
-        <v>13.96750001907349</v>
+        <v>195.5</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>26.75084160712157</v>
+        <v>41.3921246104654</v>
       </c>
       <c r="J45" t="n">
-        <v>44.10713157787018</v>
+        <v>53.56820222383845</v>
       </c>
       <c r="K45" t="n">
-        <v>31.71014168267041</v>
+        <v>41.29275289182846</v>
       </c>
       <c r="L45" t="n">
-        <v>229664.4</v>
+        <v>676814.6</v>
       </c>
       <c r="M45" t="n">
-        <v>175119.45</v>
+        <v>503017.6</v>
       </c>
       <c r="N45" t="n">
-        <v>163606.2</v>
+        <v>613194.975</v>
       </c>
       <c r="O45" t="n">
-        <v>1.311472826119543</v>
+        <v>1.345508785378484</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.07566821083075403</v>
+        <v>-2.222619674657807</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.02209096333063492</v>
+        <v>-3.365469380432589</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.05357724750011911</v>
+        <v>1.142849705774782</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.04047903126309773</v>
+        <v>2.052891996986578</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.01606940690358072</v>
+        <v>2.622598420862926</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7001,44 +7001,44 @@
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>-56</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>-62</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>-4.25</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>-15.25</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -7053,63 +7053,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>杏國</t>
+          <t>美時</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>20.20000076293945</v>
+        <v>199.5</v>
       </c>
       <c r="G46" t="n">
-        <v>20.51999998092651</v>
+        <v>195.625</v>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>47.75526385542268</v>
+        <v>48.46594830712634</v>
       </c>
       <c r="J46" t="n">
-        <v>52.71182957580636</v>
+        <v>57.18255662238658</v>
       </c>
       <c r="K46" t="n">
-        <v>46.24905879634206</v>
+        <v>51.04634985350656</v>
       </c>
       <c r="L46" t="n">
-        <v>14068.8</v>
+        <v>2843172</v>
       </c>
       <c r="M46" t="n">
-        <v>10919.65</v>
+        <v>2177997.75</v>
       </c>
       <c r="N46" t="n">
-        <v>12282.825</v>
+        <v>2123164.275</v>
       </c>
       <c r="O46" t="n">
-        <v>1.288392942997257</v>
+        <v>1.305406307237921</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.009650670969385544</v>
+        <v>0.9487212654719883</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.01256783388605599</v>
+        <v>-0.2025381129506909</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.02221850485544154</v>
+        <v>1.151259378422679</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0001565652389929756</v>
+        <v>1.508394949891886</v>
       </c>
       <c r="T46" t="n">
-        <v>0.005032901694779417</v>
+        <v>2.264618804309465</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -7143,48 +7143,48 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>-193.378</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>-30.271</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>-215.649</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>-1909.599</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>-230.51</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>-2112.109</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>-2335.375999999999</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>-41.333</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>-48.04900000000008</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>-2424.758</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -7195,67 +7195,67 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>訊聯基因</t>
+          <t>拓凱</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>41.15000152587891</v>
+        <v>168.5</v>
       </c>
       <c r="G47" t="n">
-        <v>40.51000003814697</v>
+        <v>168.075</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>46.94830249983601</v>
+        <v>40.89676480303718</v>
       </c>
       <c r="J47" t="n">
-        <v>52.68359968572608</v>
+        <v>54.9687133121155</v>
       </c>
       <c r="K47" t="n">
-        <v>51.62116164646526</v>
+        <v>53.88863689234906</v>
       </c>
       <c r="L47" t="n">
-        <v>86534.8</v>
+        <v>321017.4</v>
       </c>
       <c r="M47" t="n">
-        <v>59199.15</v>
+        <v>278832.7</v>
       </c>
       <c r="N47" t="n">
-        <v>65210.525</v>
+        <v>283881.625</v>
       </c>
       <c r="O47" t="n">
-        <v>1.461757474558334</v>
+        <v>1.151290361568066</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2361502605521437</v>
+        <v>2.62074865733041</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.008332658574372757</v>
+        <v>2.788064810470363</v>
       </c>
       <c r="R47" t="n">
-        <v>0.2444829191265165</v>
+        <v>-0.1673161531399532</v>
       </c>
       <c r="S47" t="n">
-        <v>0.3207628441051603</v>
+        <v>0.1484353951960844</v>
       </c>
       <c r="T47" t="n">
-        <v>0.3657376994629179</v>
+        <v>0.2931714037339601</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7284,53 +7284,53 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>0.709</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>361.017</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>362.726</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>181.741</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>350.203</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>532.9440000000001</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>736.1750000000002</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>419.2240000000001</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1152.399</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -7341,71 +7341,71 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>中天</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>16.14999961853027</v>
+        <v>17.5</v>
       </c>
       <c r="G48" t="n">
-        <v>16.01499991416931</v>
+        <v>17.21499977111817</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>41.96948738637866</v>
+        <v>40.09660907196812</v>
       </c>
       <c r="J48" t="n">
-        <v>54.99278296662159</v>
+        <v>26.38306608967157</v>
       </c>
       <c r="K48" t="n">
-        <v>50.56364933410666</v>
+        <v>53.47335811071496</v>
       </c>
       <c r="L48" t="n">
-        <v>5962241.8</v>
+        <v>13209362.6</v>
       </c>
       <c r="M48" t="n">
-        <v>4129132.75</v>
+        <v>17548980.55</v>
       </c>
       <c r="N48" t="n">
-        <v>2935671.625</v>
+        <v>26584215.9</v>
       </c>
       <c r="O48" t="n">
-        <v>1.443945293354882</v>
+        <v>0.7527139575067795</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5391302455212639</v>
+        <v>-0.3071179463889635</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4605675795586724</v>
+        <v>-0.2992367532296935</v>
       </c>
       <c r="R48" t="n">
-        <v>0.07856266596259143</v>
+        <v>-0.00788119315927005</v>
       </c>
       <c r="S48" t="n">
-        <v>0.1914615738139401</v>
+        <v>-0.0963320033148426</v>
       </c>
       <c r="T48" t="n">
-        <v>0.2473418355222544</v>
+        <v>-0.1436160484859784</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7439,44 +7439,44 @@
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>11112.728</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>11162.728</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>10093.407</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>10131.407</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>-37141.835</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>-79.327</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>-37221.162</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -7487,71 +7487,71 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>71.09999847412109</v>
+        <v>53.70000076293945</v>
       </c>
       <c r="G49" t="n">
-        <v>68.35000038146973</v>
+        <v>53.56499996185303</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>48.89565196107315</v>
+        <v>32.44210399191939</v>
       </c>
       <c r="J49" t="n">
-        <v>53.2416467330309</v>
+        <v>27.30035955982127</v>
       </c>
       <c r="K49" t="n">
-        <v>54.19708673510586</v>
+        <v>52.43185038930213</v>
       </c>
       <c r="L49" t="n">
-        <v>2152884</v>
+        <v>335579.6</v>
       </c>
       <c r="M49" t="n">
-        <v>1695422.5</v>
+        <v>553836.1</v>
       </c>
       <c r="N49" t="n">
-        <v>1484871.475</v>
+        <v>835341.925</v>
       </c>
       <c r="O49" t="n">
-        <v>1.269821534160364</v>
+        <v>0.6059186102169938</v>
       </c>
       <c r="P49" t="n">
-        <v>1.080763554662994</v>
+        <v>-0.1113356606951754</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.729070231850081</v>
+        <v>-0.1036829988381547</v>
       </c>
       <c r="R49" t="n">
-        <v>0.3516933228129129</v>
+        <v>-0.007652661857020682</v>
       </c>
       <c r="S49" t="n">
-        <v>0.4269541849496234</v>
+        <v>-0.05255932226349203</v>
       </c>
       <c r="T49" t="n">
-        <v>0.4816306985140936</v>
+        <v>-0.08778432179108844</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7585,44 +7585,336 @@
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>443.446</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>466.446</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>588.6940000000001</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>-11.6</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>577.0940000000001</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1902.709</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>-41.59999999999999</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1861.109</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>接近</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>合邦</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="G50" t="n">
+        <v>31.77750015258789</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>25.26022309451297</v>
+      </c>
+      <c r="J50" t="n">
+        <v>35.97148980300321</v>
+      </c>
+      <c r="K50" t="n">
+        <v>29.20195822933731</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3168.2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2251.8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1917.95</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.406963318234301</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-1.630694530498051</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-1.547443465608402</v>
+      </c>
+      <c r="R50" t="n">
+        <v>-0.08325106488964851</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.05766911139187414</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.06061038374786065</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>接近</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>力士</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>57.59999847412109</v>
+      </c>
+      <c r="G51" t="n">
+        <v>59.63499965667724</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>39.25974729824883</v>
+      </c>
+      <c r="J51" t="n">
+        <v>53.61510637891414</v>
+      </c>
+      <c r="K51" t="n">
+        <v>51.50934707778802</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2144894.6</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1720706.8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1715087.825</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.246519511633243</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3.705139629520659</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4.413824594809336</v>
+      </c>
+      <c r="R51" t="n">
+        <v>-0.7086849652886773</v>
+      </c>
+      <c r="S51" t="n">
+        <v>-0.294922584170898</v>
+      </c>
+      <c r="T51" t="n">
+        <v>-0.002713640736272893</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>

--- a/output/screening_result.xlsx
+++ b/output/screening_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN51"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>31.85000038146973</v>
+        <v>32.25</v>
       </c>
       <c r="G2" t="n">
-        <v>32.76749982833862</v>
+        <v>32.69999990463257</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>34.20116889257829</v>
+        <v>33.91189037341701</v>
       </c>
       <c r="J2" t="n">
-        <v>46.7549271938021</v>
+        <v>42.47391493129841</v>
       </c>
       <c r="K2" t="n">
-        <v>30.97104170868637</v>
+        <v>40.3061211090013</v>
       </c>
       <c r="L2" t="n">
-        <v>58835.8</v>
+        <v>59911.6</v>
       </c>
       <c r="M2" t="n">
-        <v>34890.6</v>
+        <v>35569.05</v>
       </c>
       <c r="N2" t="n">
-        <v>44255.875</v>
+        <v>44370.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.686293729543201</v>
+        <v>1.684374477249181</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2842236917777115</v>
+        <v>-0.2898672317847613</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2472639884589217</v>
+        <v>-0.2539554675269527</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03695970331878973</v>
+        <v>-0.03591176425780851</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007712216259010862</v>
+        <v>-0.03768357955493512</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03598331456728865</v>
+        <v>0.006931830600871769</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,115 +723,115 @@
         </is>
       </c>
       <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>18.506</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4</v>
-      </c>
       <c r="AM2" t="n">
-        <v>22.506</v>
+        <v>19</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>接近</t>
+          <t>符合</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金穎生技</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>32.5</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>33.30500020980835</v>
+        <v>12.34249997138977</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>37.67206186357402</v>
+        <v>41.48372377772002</v>
       </c>
       <c r="J3" t="n">
-        <v>44.94610939283048</v>
+        <v>37.54753475894721</v>
       </c>
       <c r="K3" t="n">
-        <v>44.71576286720469</v>
+        <v>41.38159472582386</v>
       </c>
       <c r="L3" t="n">
-        <v>75217.39999999999</v>
+        <v>1123315.2</v>
       </c>
       <c r="M3" t="n">
-        <v>31204.4</v>
+        <v>687040.15</v>
       </c>
       <c r="N3" t="n">
-        <v>28084.1</v>
+        <v>602091.375</v>
       </c>
       <c r="O3" t="n">
-        <v>2.410474163899963</v>
+        <v>1.635006629525217</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3693563248643272</v>
+        <v>-0.1759197956009295</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.547673755025359</v>
+        <v>-0.1550536515883049</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1783174301610317</v>
+        <v>-0.0208661440126246</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3039546998325752</v>
+        <v>-0.04023156328161681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4366870868234886</v>
+        <v>-0.02485670498199957</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>415.955</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>425.955</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>362.33</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>389.33</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1336.296</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1354.296</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>醫影</t>
+          <t>陽程</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63.70000076293945</v>
+        <v>123</v>
       </c>
       <c r="G4" t="n">
-        <v>63.83499965667725</v>
+        <v>121.475</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>39.75618934471713</v>
+        <v>37.11005066673476</v>
       </c>
       <c r="J4" t="n">
-        <v>45.83207292789818</v>
+        <v>44.29594225988522</v>
       </c>
       <c r="K4" t="n">
-        <v>46.48751437902355</v>
+        <v>49.62012325377918</v>
       </c>
       <c r="L4" t="n">
-        <v>208260.4</v>
+        <v>3611171</v>
       </c>
       <c r="M4" t="n">
-        <v>88873.2</v>
+        <v>1965536.1</v>
       </c>
       <c r="N4" t="n">
-        <v>64420.5</v>
+        <v>1884916.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34334310005716</v>
+        <v>1.837244810716018</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1477754006326819</v>
+        <v>-0.0320119468921547</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4743453567101243</v>
+        <v>-0.4621870945004286</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3265699560774424</v>
+        <v>0.4301751476082739</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4706998031646441</v>
+        <v>0.5690269758466447</v>
       </c>
       <c r="T4" t="n">
-        <v>0.567554105459778</v>
+        <v>1.107618040285628</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1067,67 +1067,67 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>陽程</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>119.5</v>
+        <v>3.150000095367432</v>
       </c>
       <c r="G5" t="n">
-        <v>121.35</v>
+        <v>3.255000007152558</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>41.83528876317562</v>
+        <v>43.56384073217421</v>
       </c>
       <c r="J5" t="n">
-        <v>47.88888800262654</v>
+        <v>43.14938156224102</v>
       </c>
       <c r="K5" t="n">
-        <v>45.89904698100938</v>
+        <v>46.6264083081478</v>
       </c>
       <c r="L5" t="n">
-        <v>3994168.2</v>
+        <v>42600</v>
       </c>
       <c r="M5" t="n">
-        <v>1955082.1</v>
+        <v>26530.25</v>
       </c>
       <c r="N5" t="n">
-        <v>1880916.9</v>
+        <v>70565.125</v>
       </c>
       <c r="O5" t="n">
-        <v>2.042966993560015</v>
+        <v>1.605714231867397</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.02961160800350626</v>
+        <v>-0.03146432999962867</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6120302320882816</v>
+        <v>-0.0007728514095954216</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5824186240847753</v>
+        <v>-0.03069147859003325</v>
       </c>
       <c r="S5" t="n">
-        <v>1.122055107980383</v>
+        <v>-0.03609424344208725</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7292870329916203</v>
+        <v>-0.04485022435676392</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1198,14 +1198,14 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>符合</t>
+          <t>接近</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>謚源</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>28.5</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>30.10249986648559</v>
+        <v>121.075</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>32.36196866560461</v>
+        <v>41.63030481144911</v>
       </c>
       <c r="J6" t="n">
-        <v>31.65241255163256</v>
+        <v>38.15877162380995</v>
       </c>
       <c r="K6" t="n">
-        <v>34.19746995871115</v>
+        <v>45.62341771723573</v>
       </c>
       <c r="L6" t="n">
-        <v>21449</v>
+        <v>9490.4</v>
       </c>
       <c r="M6" t="n">
-        <v>11115</v>
+        <v>6093.05</v>
       </c>
       <c r="N6" t="n">
-        <v>13354.425</v>
+        <v>8679.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.929734592892488</v>
+        <v>1.557577896127555</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1851556401382162</v>
+        <v>-2.296462110845383</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1412927157493716</v>
+        <v>-2.323281153696066</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.04386292438884462</v>
+        <v>0.02681904285068359</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07983922536489227</v>
+        <v>-0.1940718089717715</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02805498769514908</v>
+        <v>-0.03818913978308336</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1340,11 +1340,11 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1359,67 +1359,67 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>金穎生技</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.180000066757202</v>
+        <v>32.84999847412109</v>
       </c>
       <c r="G7" t="n">
-        <v>3.272500002384186</v>
+        <v>33.25000009536743</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>39.83555751077201</v>
+        <v>33.62044802011722</v>
       </c>
       <c r="J7" t="n">
-        <v>42.94215193331156</v>
+        <v>41.17088893836348</v>
       </c>
       <c r="K7" t="n">
-        <v>48.30974711621549</v>
+        <v>45.38853937003101</v>
       </c>
       <c r="L7" t="n">
-        <v>38200</v>
+        <v>47206.6</v>
       </c>
       <c r="M7" t="n">
-        <v>25180.25</v>
+        <v>30801.65</v>
       </c>
       <c r="N7" t="n">
-        <v>70565.125</v>
+        <v>25857.375</v>
       </c>
       <c r="O7" t="n">
-        <v>1.517061983101836</v>
+        <v>1.532599714625677</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.02833480713405523</v>
+        <v>-0.4115884051129655</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008157566339477909</v>
+        <v>-0.534175404688599</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.03649237347353314</v>
+        <v>0.1225869995756336</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.04527943442210391</v>
+        <v>0.1837464812219303</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.05067223432556733</v>
+        <v>0.3098075699416674</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1519,124 +1519,124 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>36.09999847412109</v>
+        <v>24.25</v>
       </c>
       <c r="G8" t="n">
-        <v>35.08249988555908</v>
+        <v>24.69750022888184</v>
       </c>
       <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>43.41682779810291</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.39014758237685</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38.05598280190717</v>
+      </c>
+      <c r="L8" t="n">
+        <v>132339.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>186624.65</v>
+      </c>
+      <c r="N8" t="n">
+        <v>314637.775</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7091206868974704</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.3227898140136674</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.2956429637758525</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.02714685023781488</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.04427120548729052</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.06368810779505091</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>57</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>43.88879848256521</v>
-      </c>
-      <c r="J8" t="n">
-        <v>34.26514633615096</v>
-      </c>
-      <c r="K8" t="n">
-        <v>55.01425153996799</v>
-      </c>
-      <c r="L8" t="n">
-        <v>234643</v>
-      </c>
-      <c r="M8" t="n">
-        <v>79511.3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>65380.9</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.951064817202083</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.1093109768636467</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.282460226879769</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1731492500161223</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1005374438711487</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.125891234117313</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-13</v>
-      </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>-498.095</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="AM8" t="n">
-        <v>22</v>
+        <v>-501.095</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1665,58 +1665,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10.05000019073486</v>
+        <v>67.5</v>
       </c>
       <c r="G9" t="n">
-        <v>10.17850003242493</v>
+        <v>69.99000053405761</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>22.68322382825935</v>
+        <v>37.93887714678212</v>
       </c>
       <c r="J9" t="n">
-        <v>27.40751533282922</v>
+        <v>41.0924543523795</v>
       </c>
       <c r="K9" t="n">
-        <v>48.27429996590129</v>
+        <v>38.82998867528485</v>
       </c>
       <c r="L9" t="n">
-        <v>54000</v>
+        <v>1787940.8</v>
       </c>
       <c r="M9" t="n">
-        <v>21856.85</v>
+        <v>4950304.55</v>
       </c>
       <c r="N9" t="n">
-        <v>38079.25</v>
+        <v>5175029.675</v>
       </c>
       <c r="O9" t="n">
-        <v>2.470621338390482</v>
+        <v>0.3611779400521934</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.01444919142518941</v>
+        <v>-1.70187726437959</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009160539967731474</v>
+        <v>-1.65422448073318</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.02360973139292089</v>
+        <v>-0.04765278364640979</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.02615463652838756</v>
+        <v>-0.09357327822207728</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0201010893121259</v>
+        <v>-0.1249413843358613</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1745,44 +1745,44 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>-364</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1</v>
+        <v>-2.024</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>-366.024</v>
       </c>
       <c r="AF9" t="n">
-        <v>7</v>
+        <v>124.2459999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-70.173</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1</v>
+        <v>25.735</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>79.80799999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>33.8</v>
+        <v>-28127.008</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>11504.774</v>
       </c>
       <c r="AL9" t="n">
-        <v>2</v>
+        <v>-3318.16</v>
       </c>
       <c r="AM9" t="n">
-        <v>35.8</v>
+        <v>-19940.394</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1811,53 +1811,53 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>83.80000305175781</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>81.81000061035157</v>
+        <v>10.16350002288818</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>67.48525432181248</v>
+        <v>28.13027173703201</v>
       </c>
       <c r="J10" t="n">
-        <v>67.97897101414067</v>
+        <v>27.64843415729555</v>
       </c>
       <c r="K10" t="n">
-        <v>48.11209203671847</v>
+        <v>53.27918927069018</v>
       </c>
       <c r="L10" t="n">
-        <v>60671.2</v>
+        <v>55000</v>
       </c>
       <c r="M10" t="n">
-        <v>32179.2</v>
+        <v>21306.85</v>
       </c>
       <c r="N10" t="n">
-        <v>40216.55</v>
+        <v>27279.225</v>
       </c>
       <c r="O10" t="n">
-        <v>1.885416666666667</v>
+        <v>2.581329478547979</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6153611180446887</v>
+        <v>-0.005311105246033065</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.821850428130239</v>
+        <v>0.005808918525699765</v>
       </c>
       <c r="R10" t="n">
-        <v>1.20648931008555</v>
+        <v>-0.01112002377173283</v>
       </c>
       <c r="S10" t="n">
-        <v>1.476029619625301</v>
+        <v>-0.02342876233388597</v>
       </c>
       <c r="T10" t="n">
-        <v>1.396051668012197</v>
+        <v>-0.02595954011385637</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1891,44 +1891,44 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.85</v>
+        <v>-2</v>
       </c>
       <c r="AE10" t="n">
-        <v>-4.15</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.075</v>
+        <v>-3</v>
       </c>
       <c r="AI10" t="n">
-        <v>21.075</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24.797</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.9149999999999997</v>
+        <v>-1</v>
       </c>
       <c r="AM10" t="n">
-        <v>25.712</v>
+        <v>26</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>大世科</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1957,49 +1957,49 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="G11" t="n">
-        <v>58.99000015258789</v>
+        <v>155.95</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>37.65263740402298</v>
+        <v>36.68841650186808</v>
       </c>
       <c r="J11" t="n">
-        <v>41.93440379910899</v>
+        <v>51.79160930695755</v>
       </c>
       <c r="K11" t="n">
-        <v>41.64448689393967</v>
+        <v>48.09433239099397</v>
       </c>
       <c r="L11" t="n">
-        <v>331052.4</v>
+        <v>15193554.4</v>
       </c>
       <c r="M11" t="n">
-        <v>180899.1</v>
+        <v>8004700.2</v>
       </c>
       <c r="N11" t="n">
-        <v>272971.475</v>
+        <v>11272763.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.830038955417689</v>
+        <v>1.898079131058525</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6291810146961936</v>
+        <v>7.078903191579428</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.7967228055718107</v>
+        <v>9.164872037713591</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1675417908756172</v>
+        <v>-2.085968846134163</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2637958927565475</v>
+        <v>-0.972989065851916</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2751363874559156</v>
+        <v>-0.4277048108830748</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2103,49 +2103,49 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.5</v>
+        <v>13.85000038146973</v>
       </c>
       <c r="G12" t="n">
-        <v>13.78499999046326</v>
+        <v>13.80500001907349</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>37.57267046981925</v>
+        <v>30.79557417479232</v>
       </c>
       <c r="J12" t="n">
-        <v>37.60461473589337</v>
+        <v>35.3349345889317</v>
       </c>
       <c r="K12" t="n">
-        <v>68.92595875800271</v>
+        <v>52.36563993403163</v>
       </c>
       <c r="L12" t="n">
-        <v>634708.2</v>
+        <v>689467.8</v>
       </c>
       <c r="M12" t="n">
-        <v>359733.9</v>
+        <v>371959.4</v>
       </c>
       <c r="N12" t="n">
-        <v>364984.75</v>
+        <v>373477.625</v>
       </c>
       <c r="O12" t="n">
-        <v>1.764382506069069</v>
+        <v>1.853610367152974</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2079493987880063</v>
+        <v>0.1898405722260819</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2040356100310344</v>
+        <v>0.198452865518603</v>
       </c>
       <c r="R12" t="n">
-        <v>0.003913788756971903</v>
+        <v>-0.008612293292521167</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.04397165581430373</v>
+        <v>0.004999596207795193</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.03819207047870121</v>
+        <v>-0.04280108476940717</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2183,44 +2183,44 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>66</v>
+        <v>-91</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>11.116</v>
+        <v>-16.116</v>
       </c>
       <c r="AE12" t="n">
-        <v>77.116</v>
+        <v>-107.116</v>
       </c>
       <c r="AF12" t="n">
-        <v>-6</v>
+        <v>-78</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>14.116</v>
+        <v>-2</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.116</v>
+        <v>-80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>279.9730000000001</v>
+        <v>219.673</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>18.118</v>
+        <v>4.002000000000001</v>
       </c>
       <c r="AM12" t="n">
-        <v>298.0910000000001</v>
+        <v>223.675</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>琉園</t>
+          <t>醫影</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2249,49 +2249,49 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25.79999923706055</v>
+        <v>64.59999847412109</v>
       </c>
       <c r="G13" t="n">
-        <v>26.63749980926514</v>
+        <v>63.89499950408936</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>38.62553062702429</v>
+        <v>37.99837305638525</v>
       </c>
       <c r="J13" t="n">
-        <v>53.07618117697966</v>
+        <v>43.22083965386906</v>
       </c>
       <c r="K13" t="n">
-        <v>46.39700251663071</v>
+        <v>50.03424979894026</v>
       </c>
       <c r="L13" t="n">
-        <v>874825.8</v>
+        <v>166655.4</v>
       </c>
       <c r="M13" t="n">
-        <v>259675.35</v>
+        <v>89923.14999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>147102.45</v>
+        <v>64945.475</v>
       </c>
       <c r="O13" t="n">
-        <v>3.36892123183814</v>
+        <v>1.853309186788942</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7588719716173138</v>
+        <v>-0.1232539930914811</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.767595528431706</v>
+        <v>-0.4041270839863957</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.008723556814392186</v>
+        <v>0.2808730908949146</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1983907606392513</v>
+        <v>0.3265699560774424</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4246791737939484</v>
+        <v>0.4706998031646441</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -2381,63 +2381,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>億而得</t>
+          <t>三星</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>73.59999847412109</v>
+        <v>56.40000152587891</v>
       </c>
       <c r="G14" t="n">
-        <v>82.3799991607666</v>
+        <v>55.98000030517578</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>33.60539440765977</v>
+        <v>48.75708370901529</v>
       </c>
       <c r="J14" t="n">
-        <v>50.38770062145136</v>
+        <v>34.80484572283778</v>
       </c>
       <c r="K14" t="n">
-        <v>34.47557410027768</v>
+        <v>53.05149222554883</v>
       </c>
       <c r="L14" t="n">
-        <v>384565.8</v>
+        <v>52808</v>
       </c>
       <c r="M14" t="n">
-        <v>226978.6</v>
+        <v>31508.85</v>
       </c>
       <c r="N14" t="n">
-        <v>201913.325</v>
+        <v>46809.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.694282192241912</v>
+        <v>1.675973575677945</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.288830326104119</v>
+        <v>-0.1993788452219576</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.471405681191704</v>
+        <v>-0.2765599357325782</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1825753550875855</v>
+        <v>0.07718109051062061</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9365995686792781</v>
+        <v>0.03539761187272095</v>
       </c>
       <c r="T14" t="n">
-        <v>1.425888930272709</v>
+        <v>0.02098588281087183</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2446,17 +2446,17 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2484,35 +2484,35 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>171.957</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>172.957</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>228.258</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>223.258</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -2527,63 +2527,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>毛寶</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>19.04999923706055</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>18.88000020980835</v>
+        <v>26.39000005722046</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>28.98792842759279</v>
+        <v>48.13218465616185</v>
       </c>
       <c r="J15" t="n">
-        <v>25.85435993354733</v>
+        <v>53.22404250420382</v>
       </c>
       <c r="K15" t="n">
-        <v>49.99304505721955</v>
+        <v>49.94942503407905</v>
       </c>
       <c r="L15" t="n">
-        <v>552712.8</v>
+        <v>264849.8</v>
       </c>
       <c r="M15" t="n">
-        <v>332138.85</v>
+        <v>160412.15</v>
       </c>
       <c r="N15" t="n">
-        <v>341285.6</v>
+        <v>191866.625</v>
       </c>
       <c r="O15" t="n">
-        <v>1.664101624967992</v>
+        <v>1.651058227197878</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3692426839056857</v>
+        <v>0.012165860227217</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4259374334402445</v>
+        <v>0.04004445845956878</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05669474953455877</v>
+        <v>-0.02787859823235178</v>
       </c>
       <c r="S15" t="n">
-        <v>0.008678643819726106</v>
+        <v>-0.03154990839801354</v>
       </c>
       <c r="T15" t="n">
-        <v>0.02429219497772495</v>
+        <v>0.01036562644723298</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2621,44 +2621,44 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-74</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>110.005</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>121.005</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -2673,63 +2673,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>隴華</t>
+          <t>德麥</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9.189999580383301</v>
+        <v>259</v>
       </c>
       <c r="G16" t="n">
-        <v>10.24949994087219</v>
+        <v>269.65</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>28.18173109760893</v>
+        <v>40.58943112845692</v>
       </c>
       <c r="J16" t="n">
-        <v>34.21639310751981</v>
+        <v>49.04979773718264</v>
       </c>
       <c r="K16" t="n">
-        <v>34.46499097567447</v>
+        <v>28.21355911964577</v>
       </c>
       <c r="L16" t="n">
-        <v>182849.4</v>
+        <v>54481.8</v>
       </c>
       <c r="M16" t="n">
-        <v>119690.9</v>
+        <v>34728.55</v>
       </c>
       <c r="N16" t="n">
-        <v>145805.6</v>
+        <v>34915.125</v>
       </c>
       <c r="O16" t="n">
-        <v>1.527680049193381</v>
+        <v>1.568789943720656</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.029391197859482</v>
+        <v>-0.8350519353444383</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.227866872757534</v>
+        <v>-0.23243296930334</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1984756748980518</v>
+        <v>-0.6026189660410983</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2482502348523425</v>
+        <v>0.1663579804573622</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2827185032452117</v>
+        <v>0.1077743973186242</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2738,17 +2738,17 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2776,35 +2776,35 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -2819,63 +2819,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>71.69999694824219</v>
+        <v>61.09999847412109</v>
       </c>
       <c r="G17" t="n">
-        <v>71.53499984741211</v>
+        <v>66.29999961853028</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>40.39558161920169</v>
+        <v>26.58617804039747</v>
       </c>
       <c r="J17" t="n">
-        <v>35.88024064757597</v>
+        <v>39.43310900503349</v>
       </c>
       <c r="K17" t="n">
-        <v>50.8246034843458</v>
+        <v>40.29677624754484</v>
       </c>
       <c r="L17" t="n">
-        <v>105811.6</v>
+        <v>57748450</v>
       </c>
       <c r="M17" t="n">
-        <v>69813.05</v>
+        <v>37080469.7</v>
       </c>
       <c r="N17" t="n">
-        <v>75571.55</v>
+        <v>75283074.27500001</v>
       </c>
       <c r="O17" t="n">
-        <v>1.515642132810413</v>
+        <v>1.557381836508937</v>
       </c>
       <c r="P17" t="n">
-        <v>0.02389425982818238</v>
+        <v>-0.01839440517861135</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.126289901993333</v>
+        <v>0.7554865593116581</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1501841618215154</v>
+        <v>-0.7738809644902694</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1837443075009714</v>
+        <v>-0.5013250756161022</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1931518098964864</v>
+        <v>-0.3030760512740747</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2909,48 +2909,48 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>120.606</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>-319.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>-1944.01</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>-2143.284</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>-34707.479</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>14577.471</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>-1834.23</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-21964.238</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-69797.84299999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>47434.16</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>904.6790000000002</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-21459.004</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>三星</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2979,49 +2979,49 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>55.90000152587891</v>
+        <v>838</v>
       </c>
       <c r="G18" t="n">
-        <v>55.97000026702881</v>
+        <v>877.2</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>31.46885293462732</v>
+        <v>36.07480332409347</v>
       </c>
       <c r="J18" t="n">
-        <v>27.82872676434698</v>
+        <v>53.54316981450866</v>
       </c>
       <c r="K18" t="n">
-        <v>45.19850266940327</v>
+        <v>51.80373704975541</v>
       </c>
       <c r="L18" t="n">
-        <v>47446</v>
+        <v>12342411.2</v>
       </c>
       <c r="M18" t="n">
-        <v>31478.95</v>
+        <v>8122014.05</v>
       </c>
       <c r="N18" t="n">
-        <v>46414.5</v>
+        <v>5540207.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.507229434272744</v>
+        <v>1.519624458172416</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2643640459862695</v>
+        <v>64.31670468546633</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3015713415459557</v>
+        <v>84.25440188248186</v>
       </c>
       <c r="R18" t="n">
-        <v>0.03720729555968616</v>
+        <v>-19.93769719701552</v>
       </c>
       <c r="S18" t="n">
-        <v>0.02293683951390135</v>
+        <v>-14.74852473331046</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01295446442208464</v>
+        <v>-4.192124069347727</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -3055,48 +3055,48 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>145</v>
+        <v>-2295.333</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>80.88500000000001</v>
       </c>
       <c r="AE18" t="n">
-        <v>149</v>
+        <v>-1618.448</v>
       </c>
       <c r="AF18" t="n">
-        <v>157.957</v>
+        <v>-457.3049999999998</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3807.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>-31.07299999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>158.957</v>
+        <v>3319.122</v>
       </c>
       <c r="AJ18" t="n">
-        <v>207.258</v>
+        <v>-8638.171000000002</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>11807.3</v>
       </c>
       <c r="AL18" t="n">
-        <v>-1</v>
+        <v>-733.931</v>
       </c>
       <c r="AM18" t="n">
-        <v>206.258</v>
+        <v>2435.198</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>拓凱</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3125,49 +3125,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="G19" t="n">
-        <v>116.2</v>
+        <v>168.35</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>20.45381637477141</v>
+        <v>39.96292256882522</v>
       </c>
       <c r="J19" t="n">
-        <v>21.05332618774105</v>
+        <v>49.96678309647879</v>
       </c>
       <c r="K19" t="n">
-        <v>31.6340594965926</v>
+        <v>59.75314893834937</v>
       </c>
       <c r="L19" t="n">
-        <v>22646112.6</v>
+        <v>454388</v>
       </c>
       <c r="M19" t="n">
-        <v>15129263.05</v>
+        <v>312968</v>
       </c>
       <c r="N19" t="n">
-        <v>15397070.55</v>
+        <v>287393.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.49684175132377</v>
+        <v>1.451867283556146</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.651372612345611</v>
+        <v>2.506538890230388</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3744124110647332</v>
+        <v>2.727186719873807</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.276960201280878</v>
+        <v>-0.2206478296434193</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.317489393352069</v>
+        <v>-0.1655064694529957</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.322068438919912</v>
+        <v>0.1503863518991331</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3205,44 +3205,44 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>7364.225</v>
+        <v>-130</v>
       </c>
       <c r="AC19" t="n">
-        <v>667.867</v>
+        <v>119</v>
       </c>
       <c r="AD19" t="n">
-        <v>1471.702</v>
+        <v>299.313</v>
       </c>
       <c r="AE19" t="n">
-        <v>9503.794</v>
+        <v>288.313</v>
       </c>
       <c r="AF19" t="n">
-        <v>25203.23300000001</v>
+        <v>-67.274</v>
       </c>
       <c r="AG19" t="n">
-        <v>6609.432999999999</v>
+        <v>120</v>
       </c>
       <c r="AH19" t="n">
-        <v>-230.0959999999999</v>
+        <v>649.154</v>
       </c>
       <c r="AI19" t="n">
-        <v>31582.56999999999</v>
+        <v>701.88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-10658.216</v>
+        <v>568.3650000000001</v>
       </c>
       <c r="AK19" t="n">
-        <v>39860.505</v>
+        <v>116</v>
       </c>
       <c r="AL19" t="n">
-        <v>1102.389</v>
+        <v>714.901</v>
       </c>
       <c r="AM19" t="n">
-        <v>30304.678</v>
+        <v>1399.266</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3271,49 +3271,49 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>63.70000076293945</v>
+        <v>109</v>
       </c>
       <c r="G20" t="n">
-        <v>66.57499961853027</v>
+        <v>115.625</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>37.05669907100165</v>
+        <v>20.77873472565562</v>
       </c>
       <c r="J20" t="n">
-        <v>45.85657453889542</v>
+        <v>20.96179569323997</v>
       </c>
       <c r="K20" t="n">
-        <v>44.79795596157779</v>
+        <v>31.6340594965926</v>
       </c>
       <c r="L20" t="n">
-        <v>53422664.2</v>
+        <v>19709233.6</v>
       </c>
       <c r="M20" t="n">
-        <v>36302274.05</v>
+        <v>14928152.4</v>
       </c>
       <c r="N20" t="n">
-        <v>74967714.15000001</v>
+        <v>14910835.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.471606548020096</v>
+        <v>1.320272802145294</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4464598078507862</v>
+        <v>-1.850916759266113</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9472419866448643</v>
+        <v>-0.6697132807050092</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.500782178794078</v>
+        <v>-1.181203478561104</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.302490773193939</v>
+        <v>-1.276960201280878</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.07824350527876467</v>
+        <v>-1.317489393352069</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3351,44 +3351,44 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>-4419.45</v>
+        <v>2585.222</v>
       </c>
       <c r="AC20" t="n">
-        <v>4289.736</v>
+        <v>-814.777</v>
       </c>
       <c r="AD20" t="n">
-        <v>840.726</v>
+        <v>-742.603</v>
       </c>
       <c r="AE20" t="n">
-        <v>711.0120000000001</v>
+        <v>1027.842</v>
       </c>
       <c r="AF20" t="n">
-        <v>-39841.055</v>
+        <v>36045.928</v>
       </c>
       <c r="AG20" t="n">
-        <v>19709.309</v>
+        <v>1489.435</v>
       </c>
       <c r="AH20" t="n">
-        <v>599.682</v>
+        <v>-1832.886</v>
       </c>
       <c r="AI20" t="n">
-        <v>-19532.064</v>
+        <v>35702.477</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-73259.255</v>
+        <v>-8634.084999999999</v>
       </c>
       <c r="AK20" t="n">
-        <v>47614.03999999999</v>
+        <v>39070.978</v>
       </c>
       <c r="AL20" t="n">
-        <v>3896.301</v>
+        <v>509.2980000000002</v>
       </c>
       <c r="AM20" t="n">
-        <v>-21748.914</v>
+        <v>30946.191</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3399,67 +3399,67 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>漢平</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>38.20000076293945</v>
+        <v>48.34999847412109</v>
       </c>
       <c r="G21" t="n">
-        <v>40.70250034332275</v>
+        <v>52.88000011444092</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>32.39430147742804</v>
+        <v>11.7143403995601</v>
       </c>
       <c r="J21" t="n">
-        <v>43.00695062211579</v>
+        <v>17.26711934926941</v>
       </c>
       <c r="K21" t="n">
-        <v>41.59021632757565</v>
+        <v>28.24639658326183</v>
       </c>
       <c r="L21" t="n">
-        <v>839854</v>
+        <v>550184.8</v>
       </c>
       <c r="M21" t="n">
-        <v>581445.55</v>
+        <v>274932.15</v>
       </c>
       <c r="N21" t="n">
-        <v>527246.775</v>
+        <v>227446.175</v>
       </c>
       <c r="O21" t="n">
-        <v>1.444424159751502</v>
+        <v>2.00116574216584</v>
       </c>
       <c r="P21" t="n">
-        <v>0.008573556890979717</v>
+        <v>-1.162084207689773</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.01894093544148001</v>
+        <v>-0.4376710677247448</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.01036737855050029</v>
+        <v>-0.7244131399650282</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2757924237688137</v>
+        <v>-0.7302137405268101</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5256952519975534</v>
+        <v>-0.7204822776022123</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3468,17 +3468,17 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3506,35 +3506,35 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>287.26</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3.945</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>291.205</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>-127.545</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>11.788</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>-115.757</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3545,16 +3545,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>中天</t>
+          <t>隆中</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3563,49 +3563,49 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15.69999980926514</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="G22" t="n">
-        <v>16.04999990463257</v>
+        <v>45.92999973297119</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>30.2018799165296</v>
+        <v>28.45141261785572</v>
       </c>
       <c r="J22" t="n">
-        <v>46.72914865134435</v>
+        <v>26.41292789953169</v>
       </c>
       <c r="K22" t="n">
-        <v>47.20932299580701</v>
+        <v>41.47579179051866</v>
       </c>
       <c r="L22" t="n">
-        <v>5148335.2</v>
+        <v>9767.200000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>4215930.7</v>
+        <v>5405.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2975898.1</v>
+        <v>8764.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.221162197945996</v>
+        <v>1.806800103592438</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4247469504033461</v>
+        <v>-0.8428569876656482</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4543180385261696</v>
+        <v>-0.6426962655443287</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.0295710881228235</v>
+        <v>-0.2001607221213195</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0782007278445227</v>
+        <v>-0.2871541468335015</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1910713809848755</v>
+        <v>-0.2660384936525523</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3691,67 +3691,67 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13.69999980926514</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="G23" t="n">
-        <v>14.18000001907349</v>
+        <v>16.61999988555908</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>33.9386509474139</v>
+        <v>43.94204938089365</v>
       </c>
       <c r="J23" t="n">
-        <v>46.73664450329568</v>
+        <v>35.81789020605312</v>
       </c>
       <c r="K23" t="n">
-        <v>48.42685200365179</v>
+        <v>48.13121804021984</v>
       </c>
       <c r="L23" t="n">
-        <v>2203071</v>
+        <v>514721.4</v>
       </c>
       <c r="M23" t="n">
-        <v>2688211.3</v>
+        <v>368561.9</v>
       </c>
       <c r="N23" t="n">
-        <v>1792966.675</v>
+        <v>455707.225</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8195304439052095</v>
+        <v>1.396567035279555</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4796668846000181</v>
+        <v>-0.4813319809120138</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.57480065939164</v>
+        <v>-0.6321337952720123</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.09513377479162199</v>
+        <v>0.1508018143599985</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0017609374454155</v>
+        <v>0.1213858658182529</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08131621380420762</v>
+        <v>0.1045902050787342</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3789,44 +3789,44 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>406.644</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>437.644</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1256.458</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1298.458</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1814.151</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>41.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1856.151</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>統領</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3855,58 +3855,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>24.54999923706055</v>
+        <v>37.75</v>
       </c>
       <c r="G24" t="n">
-        <v>22.75250015258789</v>
+        <v>37.55999984741211</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>52.31833414671451</v>
+        <v>38.46476275160994</v>
       </c>
       <c r="J24" t="n">
-        <v>34.879266309904</v>
+        <v>30.02049645267448</v>
       </c>
       <c r="K24" t="n">
-        <v>71.12345025059163</v>
+        <v>53.16928152713692</v>
       </c>
       <c r="L24" t="n">
-        <v>121156.8</v>
+        <v>97970.39999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>49302.8</v>
+        <v>74261.8</v>
       </c>
       <c r="N24" t="n">
-        <v>30357.15</v>
+        <v>99922.39999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>2.457402013678736</v>
+        <v>1.319257006967243</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2091113421501518</v>
+        <v>-0.09141023494743195</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1354173747552232</v>
+        <v>-0.08149405139269837</v>
       </c>
       <c r="R24" t="n">
-        <v>0.07369396739492864</v>
+        <v>-0.009916183554733574</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.07548873045352085</v>
+        <v>-0.04648781282929459</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.08489118665591353</v>
+        <v>-0.05398054470137051</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3935,44 +3935,44 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AE24" t="n">
-        <v>53.8</v>
+        <v>69</v>
       </c>
       <c r="AF24" t="n">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.2</v>
+        <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>57.8</v>
+        <v>133</v>
       </c>
       <c r="AJ24" t="n">
-        <v>113.224</v>
+        <v>88</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.2000000000000002</v>
+        <v>-0.2620000000000001</v>
       </c>
       <c r="AM24" t="n">
-        <v>113.024</v>
+        <v>87.738</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3987,63 +3987,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>199.5</v>
       </c>
       <c r="G25" t="n">
-        <v>77.74499969482422</v>
+        <v>202.05</v>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>77.98973441328917</v>
+        <v>38.53348509691173</v>
       </c>
       <c r="J25" t="n">
-        <v>74.41591713693958</v>
+        <v>36.45524736282951</v>
       </c>
       <c r="K25" t="n">
-        <v>53.5720281146323</v>
+        <v>47.2242896356423</v>
       </c>
       <c r="L25" t="n">
-        <v>128986.2</v>
+        <v>234658</v>
       </c>
       <c r="M25" t="n">
-        <v>57339.75</v>
+        <v>185057.2</v>
       </c>
       <c r="N25" t="n">
-        <v>62888.85</v>
+        <v>199818.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.249507540580487</v>
+        <v>1.268029560589915</v>
       </c>
       <c r="P25" t="n">
-        <v>0.03387606041756897</v>
+        <v>-1.986239691374976</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.01189584493200951</v>
+        <v>-2.298626284461632</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02198021548555946</v>
+        <v>0.3123865930866558</v>
       </c>
       <c r="S25" t="n">
-        <v>0.005357696724183507</v>
+        <v>0.2796771565051106</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.02170397707746514</v>
+        <v>0.4932155268002671</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4052,17 +4052,17 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4081,44 +4081,44 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>105.105</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>106.105</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>129.21</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>135.21</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4133,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4147,49 +4147,49 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>23.79999923706055</v>
+        <v>63.5</v>
       </c>
       <c r="G26" t="n">
-        <v>23.31750001907348</v>
+        <v>69.83500061035156</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>53.6015573620247</v>
+        <v>13.91200227483967</v>
       </c>
       <c r="J26" t="n">
-        <v>46.47206631474066</v>
+        <v>20.44270917371658</v>
       </c>
       <c r="K26" t="n">
-        <v>53.22009348054807</v>
+        <v>36.6747572208773</v>
       </c>
       <c r="L26" t="n">
-        <v>297668.2</v>
+        <v>64899586.2</v>
       </c>
       <c r="M26" t="n">
-        <v>163674.95</v>
+        <v>51307947.15</v>
       </c>
       <c r="N26" t="n">
-        <v>176643.425</v>
+        <v>58454426.15</v>
       </c>
       <c r="O26" t="n">
-        <v>1.818654595587168</v>
+        <v>1.264903193461717</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.102562553206841</v>
+        <v>0.2922307321946533</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.2270152242848617</v>
+        <v>1.498231268338968</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1244526710780207</v>
+        <v>-1.206000536144315</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1055602776801123</v>
+        <v>-1.01216491246345</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.03656496764793371</v>
+        <v>-0.7971603769465956</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4223,48 +4223,48 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>77</v>
+        <v>-1518.393</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>-2583.428</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>-256.233</v>
       </c>
       <c r="AE26" t="n">
-        <v>80</v>
+        <v>-4358.054</v>
       </c>
       <c r="AF26" t="n">
-        <v>78.69</v>
+        <v>39351.14600000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>13866.825</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.297000000000001</v>
+        <v>-10710.711</v>
       </c>
       <c r="AI26" t="n">
-        <v>82.98699999999999</v>
+        <v>42507.26</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-184.77</v>
+        <v>6340.140000000003</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>17010.911</v>
       </c>
       <c r="AL26" t="n">
-        <v>16.297</v>
+        <v>4068.526000000001</v>
       </c>
       <c r="AM26" t="n">
-        <v>-168.473</v>
+        <v>27419.577</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4279,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>友鋮</t>
+          <t>滿心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4293,49 +4293,49 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>47.5</v>
+        <v>40.5</v>
       </c>
       <c r="G27" t="n">
-        <v>47.08500022888184</v>
+        <v>41.07999973297119</v>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>45.78816273250214</v>
+        <v>36.05474158398927</v>
       </c>
       <c r="J27" t="n">
-        <v>36.14440392322234</v>
+        <v>30.09904423709164</v>
       </c>
       <c r="K27" t="n">
-        <v>53.54420837196371</v>
+        <v>33.98385063608227</v>
       </c>
       <c r="L27" t="n">
-        <v>38610</v>
+        <v>181172.6</v>
       </c>
       <c r="M27" t="n">
-        <v>22113.1</v>
+        <v>143863.05</v>
       </c>
       <c r="N27" t="n">
-        <v>30754.775</v>
+        <v>162456.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.746023850115995</v>
+        <v>1.259340741072847</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.3072768842329978</v>
+        <v>-0.8138512942327125</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.3706699505160868</v>
+        <v>-0.8598167023944095</v>
       </c>
       <c r="R27" t="n">
-        <v>0.06339306628308894</v>
+        <v>0.04596540816169703</v>
       </c>
       <c r="S27" t="n">
-        <v>0.006157129989027177</v>
+        <v>0.01459412979158192</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.01387110799574609</v>
+        <v>0.03708640660260887</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4439,49 +4439,49 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11.80000019073486</v>
+        <v>87.19999694824219</v>
       </c>
       <c r="G28" t="n">
-        <v>12.35999999046326</v>
+        <v>90.88000030517578</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>27.85058193837805</v>
+        <v>23.19257727007705</v>
       </c>
       <c r="J28" t="n">
-        <v>35.57944019519256</v>
+        <v>21.78865058759157</v>
       </c>
       <c r="K28" t="n">
-        <v>23.85582022864324</v>
+        <v>45.72414098863612</v>
       </c>
       <c r="L28" t="n">
-        <v>1118125.4</v>
+        <v>11136632.6</v>
       </c>
       <c r="M28" t="n">
-        <v>652955.1</v>
+        <v>9129005.4</v>
       </c>
       <c r="N28" t="n">
-        <v>586396.8</v>
+        <v>9384520.025</v>
       </c>
       <c r="O28" t="n">
-        <v>1.712407790367209</v>
+        <v>1.21991740743192</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.1881154541173888</v>
+        <v>-0.8372477798701681</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.1469790489922898</v>
+        <v>0.3056368168868967</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.04113640512509903</v>
+        <v>-1.142884596757065</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.02583218333351384</v>
+        <v>-1.367683385203481</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.00744795300514503</v>
+        <v>-1.203098749422033</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4515,48 +4515,48 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>48.41</v>
+        <v>4070.99</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>272.773</v>
       </c>
       <c r="AE28" t="n">
-        <v>70.41</v>
+        <v>4432.763</v>
       </c>
       <c r="AF28" t="n">
-        <v>30.849</v>
+        <v>9953.447</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1016.75</v>
       </c>
       <c r="AH28" t="n">
-        <v>15</v>
+        <v>-4961.32</v>
       </c>
       <c r="AI28" t="n">
-        <v>45.849</v>
+        <v>6008.876999999997</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000.841</v>
+        <v>-19101.821</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>15463.864</v>
       </c>
       <c r="AL28" t="n">
-        <v>23</v>
+        <v>-3410.106000000001</v>
       </c>
       <c r="AM28" t="n">
-        <v>1023.841</v>
+        <v>-7048.062999999999</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4585,53 +4585,53 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>20.54999923706055</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>21.02749977111817</v>
+        <v>36.33250007629395</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>35.50275097973773</v>
+        <v>45.18087064890248</v>
       </c>
       <c r="J29" t="n">
-        <v>44.27420908322494</v>
+        <v>31.62153651282727</v>
       </c>
       <c r="K29" t="n">
-        <v>39.48459134939345</v>
+        <v>54.37803088876467</v>
       </c>
       <c r="L29" t="n">
-        <v>256059.6</v>
+        <v>65983.8</v>
       </c>
       <c r="M29" t="n">
-        <v>187166.65</v>
+        <v>129120.65</v>
       </c>
       <c r="N29" t="n">
-        <v>203448.175</v>
+        <v>197427.025</v>
       </c>
       <c r="O29" t="n">
-        <v>1.368083469998528</v>
+        <v>0.511024379136877</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.07867396908310553</v>
+        <v>-0.07002313896768442</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.009820819643671187</v>
+        <v>-0.04822491630489149</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.08849478872677671</v>
+        <v>-0.02179822266279292</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.08625040128160988</v>
+        <v>-0.1008713412076544</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.08610241774491934</v>
+        <v>-0.1365157406023146</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4665,44 +4665,44 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="AE29" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="AF29" t="n">
-        <v>-46.651</v>
+        <v>133</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="AI29" t="n">
-        <v>-34.651</v>
+        <v>128</v>
       </c>
       <c r="AJ29" t="n">
-        <v>399.974</v>
+        <v>301.444</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>12</v>
+        <v>-3</v>
       </c>
       <c r="AM29" t="n">
-        <v>411.974</v>
+        <v>298.444</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -4717,67 +4717,67 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>集雅社</t>
+          <t>全坤建</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>47.5</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>48.44249992370605</v>
+        <v>13.39500002861023</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>46.27930819189135</v>
+        <v>31.86313393420843</v>
       </c>
       <c r="J30" t="n">
-        <v>45.93871171290229</v>
+        <v>33.70703004178134</v>
       </c>
       <c r="K30" t="n">
-        <v>45.00479107739616</v>
+        <v>50.38641942878996</v>
       </c>
       <c r="L30" t="n">
-        <v>8408</v>
+        <v>81432.60000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>6412.5</v>
+        <v>161517.4</v>
       </c>
       <c r="N30" t="n">
-        <v>7578.1</v>
+        <v>252133.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.311189083820663</v>
+        <v>0.504172305893978</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.05407916947116576</v>
+        <v>-0.02965306827339376</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1147914030646107</v>
+        <v>-0.003031956268552638</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.1688705725357765</v>
+        <v>-0.02662111200484112</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.1718931646304488</v>
+        <v>-0.03852077573993826</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.1748044844676204</v>
+        <v>-0.04415525656733409</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4811,44 +4811,44 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>115.08</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>108.08</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -4859,67 +4859,67 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>台驊控股</t>
+          <t>謚源</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>68.59999847412109</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="G31" t="n">
-        <v>70.11499938964843</v>
+        <v>29.98749990463257</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>32.65212882343811</v>
+        <v>27.5575588683257</v>
       </c>
       <c r="J31" t="n">
-        <v>47.77370018838155</v>
+        <v>30.28746136669922</v>
       </c>
       <c r="K31" t="n">
-        <v>42.12656051296092</v>
+        <v>29.43940986723329</v>
       </c>
       <c r="L31" t="n">
-        <v>501949</v>
+        <v>31803.6</v>
       </c>
       <c r="M31" t="n">
-        <v>399457.85</v>
+        <v>13304.2</v>
       </c>
       <c r="N31" t="n">
-        <v>447426.05</v>
+        <v>14573.625</v>
       </c>
       <c r="O31" t="n">
-        <v>1.256575631196132</v>
+        <v>2.39049322770253</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1920271019665734</v>
+        <v>-0.3523722307682817</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.3997653089392494</v>
+        <v>-0.1835086187531536</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.2077382069726761</v>
+        <v>-0.1688636120151281</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.09544905314606311</v>
+        <v>-0.04386292438884462</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.02688382498001063</v>
+        <v>0.07983922536489227</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4928,17 +4928,17 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4957,44 +4957,44 @@
         </is>
       </c>
       <c r="AB31" t="n">
-        <v>-391.803</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>31.545</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-360.258</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>-699.205</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>17.54</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-681.6650000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-542.888</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>227.971</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>-312.9169999999999</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -5005,71 +5005,71 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>黑松</t>
+          <t>太醫</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>33.45000076293945</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="G32" t="n">
-        <v>33.96000022888184</v>
+        <v>80.44000053405762</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>53.96026134500078</v>
+        <v>39.02996711015018</v>
       </c>
       <c r="J32" t="n">
-        <v>34.01076517558803</v>
+        <v>51.01941648107569</v>
       </c>
       <c r="K32" t="n">
-        <v>40.35990083763099</v>
+        <v>29.41519428778686</v>
       </c>
       <c r="L32" t="n">
-        <v>136548.4</v>
+        <v>67408.39999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>173892.25</v>
+        <v>40991.85</v>
       </c>
       <c r="N32" t="n">
-        <v>164706.275</v>
+        <v>44578.1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7852471861166901</v>
+        <v>1.644434198505313</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.4089827947953495</v>
+        <v>0.06000662606406593</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.3722496847097924</v>
+        <v>0.2489184952209048</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.03673311008555713</v>
+        <v>-0.1889118691568389</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.07329473773370659</v>
+        <v>0.07052150618557945</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.1049431988587589</v>
+        <v>0.07713885242037205</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -5079,22 +5079,22 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5103,44 +5103,44 @@
         </is>
       </c>
       <c r="AB32" t="n">
-        <v>103.35</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>117.35</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>230.972</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>-2.388</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>228.584</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>550.992</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.575000000000002</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>554.5669999999999</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -5151,16 +5151,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>潤隆</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5169,53 +5169,53 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>30.70000076293945</v>
+        <v>111</v>
       </c>
       <c r="G33" t="n">
-        <v>30.67250003814697</v>
+        <v>119.695000076294</v>
       </c>
       <c r="H33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>42.50343264356408</v>
+        <v>31.83626329506109</v>
       </c>
       <c r="J33" t="n">
-        <v>37.17541551991434</v>
+        <v>47.69128882626439</v>
       </c>
       <c r="K33" t="n">
-        <v>51.79055752878181</v>
+        <v>50.75887246342118</v>
       </c>
       <c r="L33" t="n">
-        <v>533680.2</v>
+        <v>6416999.2</v>
       </c>
       <c r="M33" t="n">
-        <v>1231814.85</v>
+        <v>4463168.95</v>
       </c>
       <c r="N33" t="n">
-        <v>1647775.675</v>
+        <v>4336851.925</v>
       </c>
       <c r="O33" t="n">
-        <v>0.43324709066464</v>
+        <v>1.437767485812967</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001413675603004094</v>
+        <v>10.25963437905079</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.03556898882842529</v>
+        <v>13.17203969112867</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.0341553132254212</v>
+        <v>-2.912405312077873</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.06490108025545367</v>
+        <v>-1.830669460735335</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.1193496947372072</v>
+        <v>-0.8666096851103848</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5249,44 +5249,44 @@
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>370.419</v>
+        <v>-1135</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>29</v>
+        <v>-6.986</v>
       </c>
       <c r="AE33" t="n">
-        <v>399.419</v>
+        <v>-1141.986</v>
       </c>
       <c r="AF33" t="n">
-        <v>501.5369999999999</v>
+        <v>-1831.524</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>10</v>
+        <v>-219.386</v>
       </c>
       <c r="AI33" t="n">
-        <v>511.5369999999999</v>
+        <v>-2050.91</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-1319.16</v>
+        <v>-892.4649999999999</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>-71.78800000000001</v>
       </c>
       <c r="AM33" t="n">
-        <v>-1283.16</v>
+        <v>-964.253</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -5301,12 +5301,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>鐿鈦</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5315,49 +5315,49 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>127</v>
+        <v>38.54999923706055</v>
       </c>
       <c r="G34" t="n">
-        <v>125.1</v>
+        <v>40.59750022888183</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>27.05385043587792</v>
+        <v>26.67234193780141</v>
       </c>
       <c r="J34" t="n">
-        <v>38.7579810159428</v>
+        <v>37.56208106812734</v>
       </c>
       <c r="K34" t="n">
-        <v>53.61488562249074</v>
+        <v>43.04648529491961</v>
       </c>
       <c r="L34" t="n">
-        <v>441103</v>
+        <v>784444.2</v>
       </c>
       <c r="M34" t="n">
-        <v>238821.9</v>
+        <v>577785.6</v>
       </c>
       <c r="N34" t="n">
-        <v>261280.2</v>
+        <v>526132.75</v>
       </c>
       <c r="O34" t="n">
-        <v>1.846995606349334</v>
+        <v>1.357673503804872</v>
       </c>
       <c r="P34" t="n">
-        <v>3.22970732589684</v>
+        <v>-0.1862158093862973</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.580951940150844</v>
+        <v>-0.01751750697549698</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.3512446142540044</v>
+        <v>-0.1686983024108004</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.1723710359814543</v>
+        <v>-0.01217706223746633</v>
       </c>
       <c r="T34" t="n">
-        <v>0.1758844691814501</v>
+        <v>0.2738414670657832</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -5447,12 +5447,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>農林</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5461,49 +5461,49 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>11.19999980926514</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="G35" t="n">
-        <v>11.09499998092651</v>
+        <v>78.07500076293945</v>
       </c>
       <c r="H35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>48.47488478563373</v>
+        <v>29.22072341242735</v>
       </c>
       <c r="J35" t="n">
-        <v>54.06068394355765</v>
+        <v>38.4854475431932</v>
       </c>
       <c r="K35" t="n">
-        <v>50.73285671752497</v>
+        <v>42.67310144428703</v>
       </c>
       <c r="L35" t="n">
-        <v>7585125.2</v>
+        <v>46968.2</v>
       </c>
       <c r="M35" t="n">
-        <v>4326823.6</v>
+        <v>34756.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3770678.2</v>
+        <v>61323.075</v>
       </c>
       <c r="O35" t="n">
-        <v>1.753047015829349</v>
+        <v>1.351340387119049</v>
       </c>
       <c r="P35" t="n">
-        <v>0.06540677782030713</v>
+        <v>0.09692083409643715</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.01780102562856227</v>
+        <v>0.5820365169580334</v>
       </c>
       <c r="R35" t="n">
-        <v>0.04760575219174486</v>
+        <v>-0.4851156828615962</v>
       </c>
       <c r="S35" t="n">
-        <v>0.06747330008342553</v>
+        <v>-0.4553551722567101</v>
       </c>
       <c r="T35" t="n">
-        <v>0.09344203602972857</v>
+        <v>-0.3596560966571145</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5541,44 +5541,44 @@
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>-1156</v>
+        <v>3</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="n">
-        <v>-1053</v>
+        <v>5</v>
       </c>
       <c r="AF35" t="n">
-        <v>-8088.9</v>
+        <v>6</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>195.114</v>
+        <v>4.139</v>
       </c>
       <c r="AI35" t="n">
-        <v>-7893.786</v>
+        <v>10.139</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-2734.206</v>
+        <v>90</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>156.787</v>
+        <v>2.445</v>
       </c>
       <c r="AM35" t="n">
-        <v>-2577.418999999999</v>
+        <v>92.44499999999999</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -5593,63 +5593,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>德麥</t>
+          <t>聯邦銀</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>271.5</v>
+        <v>21.04999923706055</v>
       </c>
       <c r="G36" t="n">
-        <v>270.2</v>
+        <v>21.71995220184326</v>
       </c>
       <c r="H36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>50.35783090039538</v>
+        <v>32.97450294900109</v>
       </c>
       <c r="J36" t="n">
-        <v>53.27998098897451</v>
+        <v>53.44302190679094</v>
       </c>
       <c r="K36" t="n">
-        <v>53.66126194506403</v>
+        <v>46.40549136823649</v>
       </c>
       <c r="L36" t="n">
-        <v>46768</v>
+        <v>3769861.8</v>
       </c>
       <c r="M36" t="n">
-        <v>30761.6</v>
+        <v>3019645.5</v>
       </c>
       <c r="N36" t="n">
-        <v>33015.45</v>
+        <v>2632811.625</v>
       </c>
       <c r="O36" t="n">
-        <v>1.52033704358681</v>
+        <v>1.248445156890105</v>
       </c>
       <c r="P36" t="n">
-        <v>0.07676685366686797</v>
+        <v>0.4333866921518457</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.0932104941644277</v>
+        <v>0.5562925033164471</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1699773478312957</v>
+        <v>-0.1229058111646014</v>
       </c>
       <c r="S36" t="n">
-        <v>0.1116763107247439</v>
+        <v>-0.03681553200749321</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2149297076240732</v>
+        <v>0.03389117656966978</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5663,12 +5663,12 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5687,44 +5687,44 @@
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>-1438.78</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>-255.756</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>-1743.536</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>-5758.740999999999</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>-67</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>-9.236000000000004</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>-5834.977</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>-4051.823</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>-6.599999999999994</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>-52.94700000000002</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>-4111.37</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>海灣</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5753,49 +5753,49 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17.39999961853027</v>
+        <v>33.34999847412109</v>
       </c>
       <c r="G37" t="n">
-        <v>17.64750022888184</v>
+        <v>33.46249961853027</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>26.43640383200383</v>
+        <v>31.84388648934484</v>
       </c>
       <c r="J37" t="n">
-        <v>25.90441749903176</v>
+        <v>33.27842954023058</v>
       </c>
       <c r="K37" t="n">
-        <v>39.7811657568821</v>
+        <v>50.67693825181988</v>
       </c>
       <c r="L37" t="n">
-        <v>36000.2</v>
+        <v>1050815.8</v>
       </c>
       <c r="M37" t="n">
-        <v>25639.75</v>
+        <v>846135.75</v>
       </c>
       <c r="N37" t="n">
-        <v>26305</v>
+        <v>695104.35</v>
       </c>
       <c r="O37" t="n">
-        <v>1.40407765286323</v>
+        <v>1.241899777902068</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.1235000649601474</v>
+        <v>0.3098995912037026</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.130992488235538</v>
+        <v>0.3683036632880497</v>
       </c>
       <c r="R37" t="n">
-        <v>0.00749242327539057</v>
+        <v>-0.05840407208434711</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02332989785977685</v>
+        <v>-0.01997491282161812</v>
       </c>
       <c r="T37" t="n">
-        <v>0.03839737428956033</v>
+        <v>0.05271066466663427</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>州巧</t>
+          <t>皇鼎</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5899,49 +5899,49 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>31.14999961853027</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>30.47000017166138</v>
+        <v>13.93000001907349</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>54.55817359252779</v>
+        <v>29.53634376217927</v>
       </c>
       <c r="J38" t="n">
-        <v>53.53444536154821</v>
+        <v>34.71889915046253</v>
       </c>
       <c r="K38" t="n">
-        <v>46.52333422706964</v>
+        <v>46.13363127051607</v>
       </c>
       <c r="L38" t="n">
-        <v>1326289.8</v>
+        <v>224673.2</v>
       </c>
       <c r="M38" t="n">
-        <v>1015242.45</v>
+        <v>192524.95</v>
       </c>
       <c r="N38" t="n">
-        <v>960306.55</v>
+        <v>173603.125</v>
       </c>
       <c r="O38" t="n">
-        <v>1.306377407682273</v>
+        <v>1.166982253468966</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.6050010405152406</v>
+        <v>-0.08701027820651497</v>
       </c>
       <c r="Q38" t="n">
-        <v>-1.112159486411015</v>
+        <v>-0.04615846919762721</v>
       </c>
       <c r="R38" t="n">
-        <v>0.5071584458957745</v>
+        <v>-0.04085180900888775</v>
       </c>
       <c r="S38" t="n">
-        <v>0.5833888067955721</v>
+        <v>-0.05559918351813153</v>
       </c>
       <c r="T38" t="n">
-        <v>0.7149666758823952</v>
+        <v>-0.05359137485561743</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5979,44 +5979,44 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>-60.8</v>
+        <v>159</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE38" t="n">
-        <v>-60.8</v>
+        <v>162</v>
       </c>
       <c r="AF38" t="n">
-        <v>-2801.258</v>
+        <v>86</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.7470000000000006</v>
+        <v>-5</v>
       </c>
       <c r="AI38" t="n">
-        <v>-2802.005</v>
+        <v>81</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-1944.718</v>
+        <v>203</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AM38" t="n">
-        <v>-1945.718</v>
+        <v>208</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -6031,12 +6031,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -6045,49 +6045,49 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>83.09999847412109</v>
+        <v>38.59999847412109</v>
       </c>
       <c r="G39" t="n">
-        <v>91.17000045776368</v>
+        <v>40.14249954223633</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>15.6222161923942</v>
+        <v>26.27436297093776</v>
       </c>
       <c r="J39" t="n">
-        <v>21.08668724140624</v>
+        <v>39.92170140714808</v>
       </c>
       <c r="K39" t="n">
-        <v>35.63669587589783</v>
+        <v>35.45387266649949</v>
       </c>
       <c r="L39" t="n">
-        <v>11890314.2</v>
+        <v>290534.2</v>
       </c>
       <c r="M39" t="n">
-        <v>9102884.25</v>
+        <v>274250.35</v>
       </c>
       <c r="N39" t="n">
-        <v>9284041.775</v>
+        <v>257055.475</v>
       </c>
       <c r="O39" t="n">
-        <v>1.306213928843487</v>
+        <v>1.059375858590518</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.7763254191273177</v>
+        <v>-0.2019545510649081</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.5913579660761629</v>
+        <v>0.07036058287046709</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.367683385203481</v>
+        <v>-0.2723151339353752</v>
       </c>
       <c r="S39" t="n">
-        <v>-1.203098749422033</v>
+        <v>-0.2452501245324102</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.792372850470388</v>
+        <v>-0.1581164217164749</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6116,53 +6116,53 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>2138.149</v>
+        <v>61.041</v>
       </c>
       <c r="AC39" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1418.069</v>
+        <v>-1</v>
       </c>
       <c r="AE39" t="n">
-        <v>4182.218</v>
+        <v>60.041</v>
       </c>
       <c r="AF39" t="n">
-        <v>-4225.085000000002</v>
+        <v>33.056</v>
       </c>
       <c r="AG39" t="n">
-        <v>5168.801</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>-4892.943000000001</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="n">
-        <v>-3949.227000000002</v>
+        <v>34.056</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-21457.899</v>
+        <v>-157.672</v>
       </c>
       <c r="AK39" t="n">
-        <v>14331.86400000001</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>-3572.087</v>
+        <v>162.843</v>
       </c>
       <c r="AM39" t="n">
-        <v>-10698.122</v>
+        <v>5.170999999999992</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -6173,67 +6173,67 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>宜新實業</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>69.09999847412109</v>
+        <v>17.54999923706055</v>
       </c>
       <c r="G40" t="n">
-        <v>68.51500015258789</v>
+        <v>17.42999982833862</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>41.17795565388872</v>
+        <v>37.6966833134878</v>
       </c>
       <c r="J40" t="n">
-        <v>49.22041637763359</v>
+        <v>49.41281449183907</v>
       </c>
       <c r="K40" t="n">
-        <v>50.03715793076051</v>
+        <v>50.18559733911302</v>
       </c>
       <c r="L40" t="n">
-        <v>2192091</v>
+        <v>110559</v>
       </c>
       <c r="M40" t="n">
-        <v>1726374.3</v>
+        <v>82295.35000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>1482120.85</v>
+        <v>90772.77499999999</v>
       </c>
       <c r="O40" t="n">
-        <v>1.269765774432578</v>
+        <v>1.343441640384299</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9050747674920245</v>
+        <v>0.01157843022568983</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7468941150270112</v>
+        <v>-0.006715406902124453</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1581806524650133</v>
+        <v>0.01829383712781428</v>
       </c>
       <c r="S40" t="n">
-        <v>0.358570112539299</v>
+        <v>0.02685940898266663</v>
       </c>
       <c r="T40" t="n">
-        <v>0.4343678114903847</v>
+        <v>0.06898854479047356</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6271,44 +6271,44 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -6319,16 +6319,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6337,49 +6337,49 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8.739999771118164</v>
+        <v>84.80000305175781</v>
       </c>
       <c r="G41" t="n">
-        <v>8.597499895095826</v>
+        <v>81.95000076293945</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>33.04604739752948</v>
+        <v>60.95656687928557</v>
       </c>
       <c r="J41" t="n">
-        <v>48.71029772907877</v>
+        <v>65.6381696651641</v>
       </c>
       <c r="K41" t="n">
-        <v>53.11753170424657</v>
+        <v>50.36622452715994</v>
       </c>
       <c r="L41" t="n">
-        <v>122246655.8</v>
+        <v>47020</v>
       </c>
       <c r="M41" t="n">
-        <v>96918746.5</v>
+        <v>32066.4</v>
       </c>
       <c r="N41" t="n">
-        <v>67458918.95</v>
+        <v>39455.575</v>
       </c>
       <c r="O41" t="n">
-        <v>1.261331375143198</v>
+        <v>1.466332360352269</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3816544280014007</v>
+        <v>-0.5092299613990292</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.418195146914436</v>
+        <v>-1.566643013172512</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.03654071891303534</v>
+        <v>1.057413051773483</v>
       </c>
       <c r="S41" t="n">
-        <v>0.004433015365362669</v>
+        <v>1.209384815030134</v>
       </c>
       <c r="T41" t="n">
-        <v>0.0520182086920144</v>
+        <v>1.47915116225786</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6417,44 +6417,44 @@
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>-6527.216</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>-139.136</v>
+        <v>-1</v>
       </c>
       <c r="AE41" t="n">
-        <v>-6666.352000000001</v>
+        <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>-97891.709</v>
+        <v>20</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>-2886.069</v>
+        <v>0.306</v>
       </c>
       <c r="AI41" t="n">
-        <v>-100777.778</v>
+        <v>20.306</v>
       </c>
       <c r="AJ41" t="n">
-        <v>61443.677</v>
+        <v>23.5</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>-989.0429999999999</v>
+        <v>-0.7880000000000005</v>
       </c>
       <c r="AM41" t="n">
-        <v>60454.63400000001</v>
+        <v>22.712</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -6465,67 +6465,67 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>40.79999923706055</v>
+        <v>28.25</v>
       </c>
       <c r="G42" t="n">
-        <v>42.4375</v>
+        <v>31.77750015258789</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>28.84968609100698</v>
+        <v>25.2602230958599</v>
       </c>
       <c r="J42" t="n">
-        <v>30.44483783417952</v>
+        <v>35.97148982814588</v>
       </c>
       <c r="K42" t="n">
-        <v>49.49495224610204</v>
+        <v>28.59586670234553</v>
       </c>
       <c r="L42" t="n">
-        <v>71185871.2</v>
+        <v>3105</v>
       </c>
       <c r="M42" t="n">
-        <v>67127118.15000001</v>
+        <v>2236</v>
       </c>
       <c r="N42" t="n">
-        <v>64058538.25</v>
+        <v>1910.05</v>
       </c>
       <c r="O42" t="n">
-        <v>1.060463686835631</v>
+        <v>1.388640429338104</v>
       </c>
       <c r="P42" t="n">
-        <v>0.5200253654995137</v>
+        <v>-1.636944843735275</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.151676700608282</v>
+        <v>-1.556589269983407</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.6316513351087678</v>
+        <v>-0.08035557375186797</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.6841050237534532</v>
+        <v>0.06079063913979943</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.7245341868311621</v>
+        <v>0.06397502834354607</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6563,1356 +6563,42 @@
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45290.931</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>-2289.819</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1288.439</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>44289.55099999999</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>213984.721</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>-12935.761</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>-6568.509000000001</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>194480.451</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>357668.762</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>22280.023</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1464.943999999999</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>381413.7290000001</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>6177</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>達麗</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>46</v>
-      </c>
-      <c r="G43" t="n">
-        <v>46.09499988555908</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>52.00739241558795</v>
-      </c>
-      <c r="J43" t="n">
-        <v>42.31447174413942</v>
-      </c>
-      <c r="K43" t="n">
-        <v>52.32075166509529</v>
-      </c>
-      <c r="L43" t="n">
-        <v>845714.8</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1823142.05</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1993209.75</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0.4638776227008751</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.01446696004240522</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.0579636184341439</v>
-      </c>
-      <c r="R43" t="n">
-        <v>-0.04349665839173868</v>
-      </c>
-      <c r="S43" t="n">
-        <v>-0.08089901272128765</v>
-      </c>
-      <c r="T43" t="n">
-        <v>-0.1449896093649889</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AB43" t="n">
-        <v>332.691</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>187</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>47</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>566.691</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1132.903</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>172.81</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>24.706</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1330.419</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-3471.591</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>2078.114</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>896.9369999999999</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>-496.5399999999997</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>20</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>3022</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>威強電</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>86.30000305175781</v>
-      </c>
-      <c r="G44" t="n">
-        <v>85.35000076293946</v>
-      </c>
-      <c r="H44" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>44.46717006477275</v>
-      </c>
-      <c r="J44" t="n">
-        <v>54.74030692594214</v>
-      </c>
-      <c r="K44" t="n">
-        <v>54.39504682840241</v>
-      </c>
-      <c r="L44" t="n">
-        <v>3300048.4</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2344915.9</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2331177.275</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.407320578106874</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.648003156277042</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.796269767284429</v>
-      </c>
-      <c r="R44" t="n">
-        <v>-0.1482666110073865</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.1074890747564727</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0.2616971210450321</v>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB44" t="n">
-        <v>275.871</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>-6.825</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>269.046</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1997.672</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>-14.86</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1982.812</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>190.6989999999999</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>38.659</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>31.31699999999999</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>260.6749999999999</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>20</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>6146</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>耕興</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="G45" t="n">
-        <v>195.5</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>41.3921246104654</v>
-      </c>
-      <c r="J45" t="n">
-        <v>53.56820222383845</v>
-      </c>
-      <c r="K45" t="n">
-        <v>41.29275289182846</v>
-      </c>
-      <c r="L45" t="n">
-        <v>676814.6</v>
-      </c>
-      <c r="M45" t="n">
-        <v>503017.6</v>
-      </c>
-      <c r="N45" t="n">
-        <v>613194.975</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.345508785378484</v>
-      </c>
-      <c r="P45" t="n">
-        <v>-2.222619674657807</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-3.365469380432589</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.142849705774782</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.052891996986578</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.622598420862926</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>20</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1795</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>美時</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>199.5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>195.625</v>
-      </c>
-      <c r="H46" t="b">
-        <v>1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>48.46594830712634</v>
-      </c>
-      <c r="J46" t="n">
-        <v>57.18255662238658</v>
-      </c>
-      <c r="K46" t="n">
-        <v>51.04634985350656</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2843172</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2177997.75</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2123164.275</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.305406307237921</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0.9487212654719883</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>-0.2025381129506909</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.151259378422679</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.508394949891886</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.264618804309465</v>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AB46" t="n">
-        <v>-193.378</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>-30.271</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>-215.649</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>-1909.599</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>-230.51</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>-2112.109</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>-2335.375999999999</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>-41.333</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>-48.04900000000008</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>-2424.758</v>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>20</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>拓凱</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>168.5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>168.075</v>
-      </c>
-      <c r="H47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I47" t="n">
-        <v>40.89676480303718</v>
-      </c>
-      <c r="J47" t="n">
-        <v>54.9687133121155</v>
-      </c>
-      <c r="K47" t="n">
-        <v>53.88863689234906</v>
-      </c>
-      <c r="L47" t="n">
-        <v>321017.4</v>
-      </c>
-      <c r="M47" t="n">
-        <v>278832.7</v>
-      </c>
-      <c r="N47" t="n">
-        <v>283881.625</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.151290361568066</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.62074865733041</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.788064810470363</v>
-      </c>
-      <c r="R47" t="n">
-        <v>-0.1673161531399532</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.1484353951960844</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.2931714037339601</v>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>361.017</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>362.726</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>181.741</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>350.203</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>532.9440000000001</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>736.1750000000002</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>419.2240000000001</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1152.399</v>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>20</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>聯合再生</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G48" t="n">
-        <v>17.21499977111817</v>
-      </c>
-      <c r="H48" t="b">
-        <v>1</v>
-      </c>
-      <c r="I48" t="n">
-        <v>40.09660907196812</v>
-      </c>
-      <c r="J48" t="n">
-        <v>26.38306608967157</v>
-      </c>
-      <c r="K48" t="n">
-        <v>53.47335811071496</v>
-      </c>
-      <c r="L48" t="n">
-        <v>13209362.6</v>
-      </c>
-      <c r="M48" t="n">
-        <v>17548980.55</v>
-      </c>
-      <c r="N48" t="n">
-        <v>26584215.9</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.7527139575067795</v>
-      </c>
-      <c r="P48" t="n">
-        <v>-0.3071179463889635</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>-0.2992367532296935</v>
-      </c>
-      <c r="R48" t="n">
-        <v>-0.00788119315927005</v>
-      </c>
-      <c r="S48" t="n">
-        <v>-0.0963320033148426</v>
-      </c>
-      <c r="T48" t="n">
-        <v>-0.1436160484859784</v>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB48" t="n">
-        <v>11112.728</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>11162.728</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>10093.407</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>10131.407</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>-37141.835</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>-79.327</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>-37221.162</v>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>20</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2540</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>愛山林</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>53.70000076293945</v>
-      </c>
-      <c r="G49" t="n">
-        <v>53.56499996185303</v>
-      </c>
-      <c r="H49" t="b">
-        <v>1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>32.44210399191939</v>
-      </c>
-      <c r="J49" t="n">
-        <v>27.30035955982127</v>
-      </c>
-      <c r="K49" t="n">
-        <v>52.43185038930213</v>
-      </c>
-      <c r="L49" t="n">
-        <v>335579.6</v>
-      </c>
-      <c r="M49" t="n">
-        <v>553836.1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>835341.925</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0.6059186102169938</v>
-      </c>
-      <c r="P49" t="n">
-        <v>-0.1113356606951754</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>-0.1036829988381547</v>
-      </c>
-      <c r="R49" t="n">
-        <v>-0.007652661857020682</v>
-      </c>
-      <c r="S49" t="n">
-        <v>-0.05255932226349203</v>
-      </c>
-      <c r="T49" t="n">
-        <v>-0.08778432179108844</v>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB49" t="n">
-        <v>443.446</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>466.446</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>588.6940000000001</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>577.0940000000001</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1902.709</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>-41.59999999999999</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1861.109</v>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>10</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>6103</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>合邦</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="G50" t="n">
-        <v>31.77750015258789</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>25.26022309451297</v>
-      </c>
-      <c r="J50" t="n">
-        <v>35.97148980300321</v>
-      </c>
-      <c r="K50" t="n">
-        <v>29.20195822933731</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3168.2</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2251.8</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1917.95</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.406963318234301</v>
-      </c>
-      <c r="P50" t="n">
-        <v>-1.630694530498051</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>-1.547443465608402</v>
-      </c>
-      <c r="R50" t="n">
-        <v>-0.08325106488964851</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.05766911139187414</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0.06061038374786065</v>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>4923</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>力士</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>57.59999847412109</v>
-      </c>
-      <c r="G51" t="n">
-        <v>59.63499965667724</v>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>39.25974729824883</v>
-      </c>
-      <c r="J51" t="n">
-        <v>53.61510637891414</v>
-      </c>
-      <c r="K51" t="n">
-        <v>51.50934707778802</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2144894.6</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1720706.8</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1715087.825</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.246519511633243</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3.705139629520659</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.413824594809336</v>
-      </c>
-      <c r="R51" t="n">
-        <v>-0.7086849652886773</v>
-      </c>
-      <c r="S51" t="n">
-        <v>-0.294922584170898</v>
-      </c>
-      <c r="T51" t="n">
-        <v>-0.002713640736272893</v>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
